--- a/naeringsdata.xlsx
+++ b/naeringsdata.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://melkno-my.sharepoint.com/personal/thea_melk_no/Documents/Dokumenter/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E9B30203-A26D-4B8A-A54D-3A94B38EAE27}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{6D93FA1D-D0F2-4C21-9BB1-20C0DCB574B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{984AFBAB-3D2F-41E4-8EB7-21071508815A}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5440" uniqueCount="115">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6045" uniqueCount="115">
   <si>
     <t>Næringsstoff</t>
   </si>
@@ -406,7 +406,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -483,6 +483,13 @@
     <font>
       <sz val="11"/>
       <color theme="5"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="9" tint="-0.499984740745262"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -616,7 +623,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="53">
+  <cellXfs count="54">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -672,6 +679,7 @@
     <xf numFmtId="0" fontId="0" fillId="18" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="19" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="19" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="2" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1080,6 +1088,15 @@
       <c r="E3" s="4" t="s">
         <v>10</v>
       </c>
+      <c r="F3" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G3" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="H3" s="4" t="s">
+        <v>10</v>
+      </c>
       <c r="I3" t="s">
         <v>7</v>
       </c>
@@ -1190,7 +1207,7 @@
       <c r="E7">
         <v>2.5</v>
       </c>
-      <c r="F7" s="5">
+      <c r="F7" s="53">
         <f t="shared" si="0"/>
         <v>24</v>
       </c>
@@ -1406,7 +1423,15 @@
       <c r="E15" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="F15" s="7"/>
+      <c r="F15" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G15" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="H15" s="4" t="s">
+        <v>10</v>
+      </c>
       <c r="I15" t="s">
         <v>32</v>
       </c>
@@ -1734,7 +1759,15 @@
       <c r="E27" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="F27" s="7"/>
+      <c r="F27" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G27" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="H27" s="4" t="s">
+        <v>10</v>
+      </c>
       <c r="I27" t="s">
         <v>33</v>
       </c>
@@ -2062,7 +2095,15 @@
       <c r="E39" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="F39" s="7"/>
+      <c r="F39" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G39" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="H39" s="4" t="s">
+        <v>10</v>
+      </c>
       <c r="I39" t="s">
         <v>34</v>
       </c>
@@ -2390,8 +2431,15 @@
       <c r="E51" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="F51" s="7"/>
-      <c r="G51" s="6"/>
+      <c r="F51" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G51" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="H51" s="4" t="s">
+        <v>10</v>
+      </c>
       <c r="I51" t="s">
         <v>35</v>
       </c>
@@ -2719,7 +2767,15 @@
       <c r="E63" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="F63" s="7"/>
+      <c r="F63" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G63" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="H63" s="4" t="s">
+        <v>10</v>
+      </c>
       <c r="I63" t="s">
         <v>36</v>
       </c>
@@ -3047,7 +3103,15 @@
       <c r="E75" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="F75" s="7"/>
+      <c r="F75" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G75" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="H75" s="4" t="s">
+        <v>10</v>
+      </c>
       <c r="I75" t="s">
         <v>37</v>
       </c>
@@ -3375,7 +3439,15 @@
       <c r="E87" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="F87" s="7"/>
+      <c r="F87" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G87" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="H87" s="4" t="s">
+        <v>10</v>
+      </c>
       <c r="I87" t="s">
         <v>38</v>
       </c>
@@ -3703,7 +3775,15 @@
       <c r="E99" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="F99" s="7"/>
+      <c r="F99" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G99" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="H99" s="4" t="s">
+        <v>10</v>
+      </c>
       <c r="I99" t="s">
         <v>39</v>
       </c>
@@ -4031,7 +4111,15 @@
       <c r="E111" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="F111" s="7"/>
+      <c r="F111" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G111" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="H111" s="4" t="s">
+        <v>10</v>
+      </c>
       <c r="I111" t="s">
         <v>40</v>
       </c>
@@ -4357,6 +4445,15 @@
       <c r="E123" s="4" t="s">
         <v>10</v>
       </c>
+      <c r="F123" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G123" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="H123" s="4" t="s">
+        <v>10</v>
+      </c>
       <c r="I123" t="s">
         <v>45</v>
       </c>
@@ -4657,7 +4754,15 @@
       <c r="E135" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="F135" s="7"/>
+      <c r="F135" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G135" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="H135" s="4" t="s">
+        <v>10</v>
+      </c>
       <c r="I135" t="s">
         <v>41</v>
       </c>
@@ -4985,7 +5090,15 @@
       <c r="E147" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="F147" s="7"/>
+      <c r="F147" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G147" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="H147" s="4" t="s">
+        <v>10</v>
+      </c>
       <c r="I147" t="s">
         <v>42</v>
       </c>
@@ -5313,7 +5426,15 @@
       <c r="E159" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="F159" s="7"/>
+      <c r="F159" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G159" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="H159" s="4" t="s">
+        <v>10</v>
+      </c>
       <c r="I159" t="s">
         <v>43</v>
       </c>
@@ -5653,7 +5774,15 @@
       <c r="E171" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="F171" s="7"/>
+      <c r="F171" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G171" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="H171" s="4" t="s">
+        <v>10</v>
+      </c>
       <c r="I171" t="s">
         <v>44</v>
       </c>
@@ -5979,7 +6108,15 @@
       <c r="E183" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="F183" s="7"/>
+      <c r="F183" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G183" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="H183" s="4" t="s">
+        <v>10</v>
+      </c>
       <c r="I183" t="s">
         <v>102</v>
       </c>
@@ -6210,9 +6347,8 @@
       <c r="E191">
         <v>375</v>
       </c>
-      <c r="F191" s="7" t="e">
-        <f t="shared" si="13"/>
-        <v>#VALUE!</v>
+      <c r="F191" t="s">
+        <v>10</v>
       </c>
       <c r="G191" s="7" t="s">
         <v>23</v>
@@ -6240,9 +6376,8 @@
       <c r="E192">
         <v>800</v>
       </c>
-      <c r="F192" s="7" t="e">
-        <f t="shared" si="13"/>
-        <v>#VALUE!</v>
+      <c r="F192" t="s">
+        <v>10</v>
       </c>
       <c r="G192" s="7" t="s">
         <v>23</v>
@@ -6305,7 +6440,15 @@
       <c r="E195" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="F195" s="7"/>
+      <c r="F195" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G195" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="H195" s="4" t="s">
+        <v>10</v>
+      </c>
       <c r="I195" t="s">
         <v>103</v>
       </c>
@@ -6536,9 +6679,8 @@
       <c r="E203">
         <v>375</v>
       </c>
-      <c r="F203" s="7" t="e">
-        <f t="shared" si="14"/>
-        <v>#VALUE!</v>
+      <c r="F203" t="s">
+        <v>10</v>
       </c>
       <c r="G203" s="7" t="s">
         <v>23</v>
@@ -6566,9 +6708,8 @@
       <c r="E204">
         <v>800</v>
       </c>
-      <c r="F204" s="7" t="e">
-        <f t="shared" si="14"/>
-        <v>#VALUE!</v>
+      <c r="F204" t="s">
+        <v>10</v>
       </c>
       <c r="G204" s="7" t="s">
         <v>23</v>
@@ -6631,7 +6772,15 @@
       <c r="E207" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="F207" s="7"/>
+      <c r="F207" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G207" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="H207" s="4" t="s">
+        <v>10</v>
+      </c>
       <c r="I207" t="s">
         <v>109</v>
       </c>
@@ -6862,9 +7011,8 @@
       <c r="E215">
         <v>375</v>
       </c>
-      <c r="F215" s="7" t="e">
-        <f t="shared" si="15"/>
-        <v>#VALUE!</v>
+      <c r="F215" t="s">
+        <v>10</v>
       </c>
       <c r="G215" s="7" t="s">
         <v>23</v>
@@ -6892,9 +7040,8 @@
       <c r="E216">
         <v>800</v>
       </c>
-      <c r="F216" s="7" t="e">
-        <f t="shared" si="15"/>
-        <v>#VALUE!</v>
+      <c r="F216" t="s">
+        <v>10</v>
       </c>
       <c r="G216" s="7" t="s">
         <v>23</v>
@@ -6957,7 +7104,15 @@
       <c r="E219" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="F219" s="7"/>
+      <c r="F219" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G219" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="H219" s="4" t="s">
+        <v>10</v>
+      </c>
       <c r="I219" t="s">
         <v>108</v>
       </c>
@@ -7188,9 +7343,8 @@
       <c r="E227">
         <v>375</v>
       </c>
-      <c r="F227" s="7" t="e">
-        <f t="shared" si="16"/>
-        <v>#VALUE!</v>
+      <c r="F227" t="s">
+        <v>10</v>
       </c>
       <c r="G227" s="7" t="s">
         <v>23</v>
@@ -7218,9 +7372,8 @@
       <c r="E228">
         <v>800</v>
       </c>
-      <c r="F228" s="7" t="e">
-        <f t="shared" si="16"/>
-        <v>#VALUE!</v>
+      <c r="F228" t="s">
+        <v>10</v>
       </c>
       <c r="G228" s="7" t="s">
         <v>23</v>
@@ -7328,6 +7481,15 @@
       <c r="E3" s="4" t="s">
         <v>10</v>
       </c>
+      <c r="F3" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G3" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="H3" s="4" t="s">
+        <v>10</v>
+      </c>
       <c r="I3" t="s">
         <v>50</v>
       </c>
@@ -7618,9 +7780,15 @@
       <c r="E13">
         <v>5</v>
       </c>
-      <c r="F13" s="5"/>
-      <c r="G13" s="7"/>
-      <c r="H13" s="7"/>
+      <c r="F13" t="s">
+        <v>10</v>
+      </c>
+      <c r="G13" t="s">
+        <v>10</v>
+      </c>
+      <c r="H13" t="s">
+        <v>10</v>
+      </c>
       <c r="I13" t="s">
         <v>50</v>
       </c>
@@ -7646,6 +7814,15 @@
       <c r="E15" s="4" t="s">
         <v>10</v>
       </c>
+      <c r="F15" t="s">
+        <v>10</v>
+      </c>
+      <c r="G15" t="s">
+        <v>10</v>
+      </c>
+      <c r="H15" t="s">
+        <v>10</v>
+      </c>
       <c r="I15" t="s">
         <v>51</v>
       </c>
@@ -7971,6 +8148,15 @@
       <c r="E27" s="4" t="s">
         <v>10</v>
       </c>
+      <c r="F27" t="s">
+        <v>10</v>
+      </c>
+      <c r="G27" t="s">
+        <v>10</v>
+      </c>
+      <c r="H27" t="s">
+        <v>10</v>
+      </c>
       <c r="I27" t="s">
         <v>52</v>
       </c>
@@ -8296,6 +8482,15 @@
       <c r="E39" s="4" t="s">
         <v>10</v>
       </c>
+      <c r="F39" t="s">
+        <v>10</v>
+      </c>
+      <c r="G39" t="s">
+        <v>10</v>
+      </c>
+      <c r="H39" t="s">
+        <v>10</v>
+      </c>
       <c r="I39" t="s">
         <v>53</v>
       </c>
@@ -8586,9 +8781,15 @@
       <c r="E49">
         <v>5</v>
       </c>
-      <c r="F49" s="5"/>
-      <c r="G49" s="7"/>
-      <c r="H49" s="7"/>
+      <c r="F49" t="s">
+        <v>10</v>
+      </c>
+      <c r="G49" t="s">
+        <v>10</v>
+      </c>
+      <c r="H49" t="s">
+        <v>10</v>
+      </c>
       <c r="I49" t="s">
         <v>53</v>
       </c>
@@ -8614,6 +8815,15 @@
       <c r="E51" s="4" t="s">
         <v>10</v>
       </c>
+      <c r="F51" t="s">
+        <v>10</v>
+      </c>
+      <c r="G51" t="s">
+        <v>10</v>
+      </c>
+      <c r="H51" t="s">
+        <v>10</v>
+      </c>
       <c r="I51" t="s">
         <v>111</v>
       </c>
@@ -8904,9 +9114,15 @@
       <c r="E61">
         <v>5</v>
       </c>
-      <c r="F61" s="5"/>
-      <c r="G61" s="7"/>
-      <c r="H61" s="7"/>
+      <c r="F61" t="s">
+        <v>10</v>
+      </c>
+      <c r="G61" t="s">
+        <v>10</v>
+      </c>
+      <c r="H61" t="s">
+        <v>10</v>
+      </c>
       <c r="I61" t="s">
         <v>111</v>
       </c>
@@ -8932,6 +9148,15 @@
       <c r="E63" s="4" t="s">
         <v>10</v>
       </c>
+      <c r="F63" t="s">
+        <v>10</v>
+      </c>
+      <c r="G63" t="s">
+        <v>10</v>
+      </c>
+      <c r="H63" t="s">
+        <v>10</v>
+      </c>
       <c r="I63" t="s">
         <v>112</v>
       </c>
@@ -9222,9 +9447,15 @@
       <c r="E73">
         <v>5</v>
       </c>
-      <c r="F73" s="5"/>
-      <c r="G73" s="7"/>
-      <c r="H73" s="7"/>
+      <c r="F73" t="s">
+        <v>10</v>
+      </c>
+      <c r="G73" t="s">
+        <v>10</v>
+      </c>
+      <c r="H73" t="s">
+        <v>10</v>
+      </c>
       <c r="I73" t="s">
         <v>112</v>
       </c>
@@ -9250,6 +9481,15 @@
       <c r="E75" s="4" t="s">
         <v>10</v>
       </c>
+      <c r="F75" t="s">
+        <v>10</v>
+      </c>
+      <c r="G75" t="s">
+        <v>10</v>
+      </c>
+      <c r="H75" t="s">
+        <v>10</v>
+      </c>
       <c r="I75" t="s">
         <v>113</v>
       </c>
@@ -9540,9 +9780,15 @@
       <c r="E85">
         <v>5</v>
       </c>
-      <c r="F85" s="5"/>
-      <c r="G85" s="7"/>
-      <c r="H85" s="7"/>
+      <c r="F85" t="s">
+        <v>10</v>
+      </c>
+      <c r="G85" t="s">
+        <v>10</v>
+      </c>
+      <c r="H85" t="s">
+        <v>10</v>
+      </c>
       <c r="I85" t="s">
         <v>113</v>
       </c>
@@ -9568,6 +9814,15 @@
       <c r="E87" s="4" t="s">
         <v>10</v>
       </c>
+      <c r="F87" t="s">
+        <v>10</v>
+      </c>
+      <c r="G87" t="s">
+        <v>10</v>
+      </c>
+      <c r="H87" t="s">
+        <v>10</v>
+      </c>
       <c r="I87" t="s">
         <v>54</v>
       </c>
@@ -9648,12 +9903,15 @@
       <c r="E90">
         <v>150</v>
       </c>
-      <c r="F90" s="5" t="e">
-        <f t="shared" ref="F90:F96" si="7">(B90/E90)*100</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="G90" s="5"/>
-      <c r="H90" s="5"/>
+      <c r="F90" t="s">
+        <v>10</v>
+      </c>
+      <c r="G90" t="s">
+        <v>10</v>
+      </c>
+      <c r="H90" t="s">
+        <v>10</v>
+      </c>
       <c r="I90" t="s">
         <v>54</v>
       </c>
@@ -9674,12 +9932,15 @@
       <c r="E91">
         <v>2.5</v>
       </c>
-      <c r="F91" s="5" t="e">
-        <f t="shared" si="7"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="G91" s="5"/>
-      <c r="H91" s="5"/>
+      <c r="F91" t="s">
+        <v>10</v>
+      </c>
+      <c r="G91" t="s">
+        <v>10</v>
+      </c>
+      <c r="H91" t="s">
+        <v>10</v>
+      </c>
       <c r="I91" t="s">
         <v>54</v>
       </c>
@@ -9700,12 +9961,15 @@
       <c r="E92">
         <v>1.4</v>
       </c>
-      <c r="F92" s="5" t="e">
-        <f t="shared" si="7"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="G92" s="5"/>
-      <c r="H92" s="5"/>
+      <c r="F92" t="s">
+        <v>10</v>
+      </c>
+      <c r="G92" t="s">
+        <v>10</v>
+      </c>
+      <c r="H92" t="s">
+        <v>10</v>
+      </c>
       <c r="I92" t="s">
         <v>54</v>
       </c>
@@ -9726,12 +9990,15 @@
       <c r="E93">
         <v>700</v>
       </c>
-      <c r="F93" s="5" t="e">
-        <f t="shared" si="7"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="G93" s="5"/>
-      <c r="H93" s="5"/>
+      <c r="F93" t="s">
+        <v>10</v>
+      </c>
+      <c r="G93" t="s">
+        <v>10</v>
+      </c>
+      <c r="H93" t="s">
+        <v>10</v>
+      </c>
       <c r="I93" t="s">
         <v>54</v>
       </c>
@@ -9752,12 +10019,15 @@
       <c r="E94">
         <v>2000</v>
       </c>
-      <c r="F94" s="5" t="e">
-        <f t="shared" si="7"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="G94" s="5"/>
-      <c r="H94" s="5"/>
+      <c r="F94" t="s">
+        <v>10</v>
+      </c>
+      <c r="G94" t="s">
+        <v>10</v>
+      </c>
+      <c r="H94" t="s">
+        <v>10</v>
+      </c>
       <c r="I94" t="s">
         <v>54</v>
       </c>
@@ -9778,12 +10048,15 @@
       <c r="E95">
         <v>375</v>
       </c>
-      <c r="F95" s="5" t="e">
-        <f t="shared" si="7"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="G95" s="5"/>
-      <c r="H95" s="7"/>
+      <c r="F95" t="s">
+        <v>10</v>
+      </c>
+      <c r="G95" t="s">
+        <v>10</v>
+      </c>
+      <c r="H95" t="s">
+        <v>10</v>
+      </c>
       <c r="I95" t="s">
         <v>54</v>
       </c>
@@ -9804,12 +10077,15 @@
       <c r="E96">
         <v>800</v>
       </c>
-      <c r="F96" s="5" t="e">
-        <f t="shared" si="7"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="G96" s="5"/>
-      <c r="H96" s="5"/>
+      <c r="F96" t="s">
+        <v>10</v>
+      </c>
+      <c r="G96" t="s">
+        <v>10</v>
+      </c>
+      <c r="H96" t="s">
+        <v>10</v>
+      </c>
       <c r="I96" t="s">
         <v>54</v>
       </c>
@@ -9830,9 +10106,15 @@
       <c r="E97">
         <v>5</v>
       </c>
-      <c r="F97" s="5"/>
-      <c r="G97" s="7"/>
-      <c r="H97" s="7"/>
+      <c r="F97" t="s">
+        <v>10</v>
+      </c>
+      <c r="G97" t="s">
+        <v>10</v>
+      </c>
+      <c r="H97" t="s">
+        <v>10</v>
+      </c>
       <c r="I97" t="s">
         <v>54</v>
       </c>
@@ -9858,6 +10140,15 @@
       <c r="E99" s="4" t="s">
         <v>10</v>
       </c>
+      <c r="F99" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G99" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="H99" s="4" t="s">
+        <v>10</v>
+      </c>
       <c r="I99" t="s">
         <v>55</v>
       </c>
@@ -9938,12 +10229,15 @@
       <c r="E102">
         <v>150</v>
       </c>
-      <c r="F102" s="5" t="e">
-        <f t="shared" ref="F102:F108" si="8">(B102/E102)*100</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="G102" s="5"/>
-      <c r="H102" s="5"/>
+      <c r="F102" t="s">
+        <v>10</v>
+      </c>
+      <c r="G102" t="s">
+        <v>10</v>
+      </c>
+      <c r="H102" t="s">
+        <v>10</v>
+      </c>
       <c r="I102" t="s">
         <v>55</v>
       </c>
@@ -9964,12 +10258,15 @@
       <c r="E103">
         <v>2.5</v>
       </c>
-      <c r="F103" s="5" t="e">
-        <f t="shared" si="8"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="G103" s="5"/>
-      <c r="H103" s="5"/>
+      <c r="F103" t="s">
+        <v>10</v>
+      </c>
+      <c r="G103" t="s">
+        <v>10</v>
+      </c>
+      <c r="H103" t="s">
+        <v>10</v>
+      </c>
       <c r="I103" t="s">
         <v>55</v>
       </c>
@@ -9990,12 +10287,15 @@
       <c r="E104">
         <v>1.4</v>
       </c>
-      <c r="F104" s="5" t="e">
-        <f t="shared" si="8"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="G104" s="5"/>
-      <c r="H104" s="5"/>
+      <c r="F104" t="s">
+        <v>10</v>
+      </c>
+      <c r="G104" t="s">
+        <v>10</v>
+      </c>
+      <c r="H104" t="s">
+        <v>10</v>
+      </c>
       <c r="I104" t="s">
         <v>55</v>
       </c>
@@ -10016,12 +10316,15 @@
       <c r="E105">
         <v>700</v>
       </c>
-      <c r="F105" s="5" t="e">
-        <f t="shared" si="8"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="G105" s="5"/>
-      <c r="H105" s="5"/>
+      <c r="F105" t="s">
+        <v>10</v>
+      </c>
+      <c r="G105" t="s">
+        <v>10</v>
+      </c>
+      <c r="H105" t="s">
+        <v>10</v>
+      </c>
       <c r="I105" t="s">
         <v>55</v>
       </c>
@@ -10042,12 +10345,15 @@
       <c r="E106">
         <v>2000</v>
       </c>
-      <c r="F106" s="5" t="e">
-        <f t="shared" si="8"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="G106" s="5"/>
-      <c r="H106" s="5"/>
+      <c r="F106" t="s">
+        <v>10</v>
+      </c>
+      <c r="G106" t="s">
+        <v>10</v>
+      </c>
+      <c r="H106" t="s">
+        <v>10</v>
+      </c>
       <c r="I106" t="s">
         <v>55</v>
       </c>
@@ -10068,12 +10374,15 @@
       <c r="E107">
         <v>375</v>
       </c>
-      <c r="F107" s="5" t="e">
-        <f t="shared" si="8"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="G107" s="5"/>
-      <c r="H107" s="7"/>
+      <c r="F107" t="s">
+        <v>10</v>
+      </c>
+      <c r="G107" t="s">
+        <v>10</v>
+      </c>
+      <c r="H107" t="s">
+        <v>10</v>
+      </c>
       <c r="I107" t="s">
         <v>55</v>
       </c>
@@ -10094,12 +10403,15 @@
       <c r="E108">
         <v>800</v>
       </c>
-      <c r="F108" s="5" t="e">
-        <f t="shared" si="8"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="G108" s="5"/>
-      <c r="H108" s="5"/>
+      <c r="F108" t="s">
+        <v>10</v>
+      </c>
+      <c r="G108" t="s">
+        <v>10</v>
+      </c>
+      <c r="H108" t="s">
+        <v>10</v>
+      </c>
       <c r="I108" t="s">
         <v>55</v>
       </c>
@@ -10120,9 +10432,15 @@
       <c r="E109">
         <v>5</v>
       </c>
-      <c r="F109" s="5"/>
-      <c r="G109" s="7"/>
-      <c r="H109" s="7"/>
+      <c r="F109" t="s">
+        <v>10</v>
+      </c>
+      <c r="G109" t="s">
+        <v>10</v>
+      </c>
+      <c r="H109" t="s">
+        <v>10</v>
+      </c>
       <c r="I109" t="s">
         <v>55</v>
       </c>
@@ -10148,6 +10466,15 @@
       <c r="E111" s="4" t="s">
         <v>10</v>
       </c>
+      <c r="F111" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G111" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="H111" s="4" t="s">
+        <v>10</v>
+      </c>
       <c r="I111" t="s">
         <v>56</v>
       </c>
@@ -10228,12 +10555,15 @@
       <c r="E114">
         <v>150</v>
       </c>
-      <c r="F114" s="5" t="e">
-        <f t="shared" ref="F114:F120" si="9">(B114/E114)*100</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="G114" s="5"/>
-      <c r="H114" s="5"/>
+      <c r="F114" t="s">
+        <v>10</v>
+      </c>
+      <c r="G114" t="s">
+        <v>10</v>
+      </c>
+      <c r="H114" t="s">
+        <v>10</v>
+      </c>
       <c r="I114" t="s">
         <v>56</v>
       </c>
@@ -10254,12 +10584,15 @@
       <c r="E115">
         <v>2.5</v>
       </c>
-      <c r="F115" s="5" t="e">
-        <f t="shared" si="9"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="G115" s="5"/>
-      <c r="H115" s="5"/>
+      <c r="F115" t="s">
+        <v>10</v>
+      </c>
+      <c r="G115" t="s">
+        <v>10</v>
+      </c>
+      <c r="H115" t="s">
+        <v>10</v>
+      </c>
       <c r="I115" t="s">
         <v>56</v>
       </c>
@@ -10280,12 +10613,15 @@
       <c r="E116">
         <v>1.4</v>
       </c>
-      <c r="F116" s="5" t="e">
-        <f t="shared" si="9"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="G116" s="5"/>
-      <c r="H116" s="5"/>
+      <c r="F116" t="s">
+        <v>10</v>
+      </c>
+      <c r="G116" t="s">
+        <v>10</v>
+      </c>
+      <c r="H116" t="s">
+        <v>10</v>
+      </c>
       <c r="I116" t="s">
         <v>56</v>
       </c>
@@ -10306,12 +10642,15 @@
       <c r="E117">
         <v>700</v>
       </c>
-      <c r="F117" s="5" t="e">
-        <f t="shared" si="9"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="G117" s="5"/>
-      <c r="H117" s="5"/>
+      <c r="F117" t="s">
+        <v>10</v>
+      </c>
+      <c r="G117" t="s">
+        <v>10</v>
+      </c>
+      <c r="H117" t="s">
+        <v>10</v>
+      </c>
       <c r="I117" t="s">
         <v>56</v>
       </c>
@@ -10332,12 +10671,15 @@
       <c r="E118">
         <v>2000</v>
       </c>
-      <c r="F118" s="5" t="e">
-        <f t="shared" si="9"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="G118" s="5"/>
-      <c r="H118" s="5"/>
+      <c r="F118" t="s">
+        <v>10</v>
+      </c>
+      <c r="G118" t="s">
+        <v>10</v>
+      </c>
+      <c r="H118" t="s">
+        <v>10</v>
+      </c>
       <c r="I118" t="s">
         <v>56</v>
       </c>
@@ -10358,12 +10700,15 @@
       <c r="E119">
         <v>375</v>
       </c>
-      <c r="F119" s="5" t="e">
-        <f t="shared" si="9"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="G119" s="5"/>
-      <c r="H119" s="7"/>
+      <c r="F119" t="s">
+        <v>10</v>
+      </c>
+      <c r="G119" t="s">
+        <v>10</v>
+      </c>
+      <c r="H119" t="s">
+        <v>10</v>
+      </c>
       <c r="I119" t="s">
         <v>56</v>
       </c>
@@ -10384,12 +10729,15 @@
       <c r="E120">
         <v>800</v>
       </c>
-      <c r="F120" s="5" t="e">
-        <f t="shared" si="9"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="G120" s="5"/>
-      <c r="H120" s="5"/>
+      <c r="F120" t="s">
+        <v>10</v>
+      </c>
+      <c r="G120" t="s">
+        <v>10</v>
+      </c>
+      <c r="H120" t="s">
+        <v>10</v>
+      </c>
       <c r="I120" t="s">
         <v>56</v>
       </c>
@@ -10410,9 +10758,15 @@
       <c r="E121">
         <v>5</v>
       </c>
-      <c r="F121" s="5"/>
-      <c r="G121" s="7"/>
-      <c r="H121" s="7"/>
+      <c r="F121" t="s">
+        <v>10</v>
+      </c>
+      <c r="G121" t="s">
+        <v>10</v>
+      </c>
+      <c r="H121" t="s">
+        <v>10</v>
+      </c>
       <c r="I121" t="s">
         <v>56</v>
       </c>
@@ -10438,6 +10792,15 @@
       <c r="E123" s="4" t="s">
         <v>10</v>
       </c>
+      <c r="F123" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G123" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="H123" s="4" t="s">
+        <v>10</v>
+      </c>
       <c r="I123" t="s">
         <v>57</v>
       </c>
@@ -10519,7 +10882,7 @@
         <v>150</v>
       </c>
       <c r="F126" s="5">
-        <f t="shared" ref="F126:F132" si="10">(B126/E126)*100</f>
+        <f t="shared" ref="F126:F133" si="7">(B126/E126)*100</f>
         <v>46.666666666666664</v>
       </c>
       <c r="G126" s="5" t="s">
@@ -10548,12 +10911,15 @@
       <c r="E127">
         <v>2.5</v>
       </c>
-      <c r="F127" s="5" t="e">
-        <f t="shared" si="10"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="G127" s="5"/>
-      <c r="H127" s="5"/>
+      <c r="F127" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G127" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="H127" s="4" t="s">
+        <v>10</v>
+      </c>
       <c r="I127" t="s">
         <v>57</v>
       </c>
@@ -10575,7 +10941,7 @@
         <v>1.4</v>
       </c>
       <c r="F128" s="5">
-        <f t="shared" si="10"/>
+        <f t="shared" si="7"/>
         <v>61.428571428571431</v>
       </c>
       <c r="G128" s="5" t="s">
@@ -10604,12 +10970,15 @@
       <c r="E129">
         <v>700</v>
       </c>
-      <c r="F129" s="5" t="e">
-        <f t="shared" si="10"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="G129" s="5"/>
-      <c r="H129" s="5"/>
+      <c r="F129" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G129" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="H129" s="4" t="s">
+        <v>10</v>
+      </c>
       <c r="I129" t="s">
         <v>57</v>
       </c>
@@ -10631,7 +11000,7 @@
         <v>2000</v>
       </c>
       <c r="F130" s="5">
-        <f t="shared" si="10"/>
+        <f t="shared" si="7"/>
         <v>65</v>
       </c>
       <c r="G130" s="5" t="s">
@@ -10660,12 +11029,15 @@
       <c r="E131">
         <v>375</v>
       </c>
-      <c r="F131" s="5" t="e">
-        <f t="shared" si="10"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="G131" s="5"/>
-      <c r="H131" s="7"/>
+      <c r="F131" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G131" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="H131" s="4" t="s">
+        <v>10</v>
+      </c>
       <c r="I131" t="s">
         <v>57</v>
       </c>
@@ -10686,12 +11058,15 @@
       <c r="E132">
         <v>800</v>
       </c>
-      <c r="F132" s="5" t="e">
-        <f t="shared" si="10"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="G132" s="5"/>
-      <c r="H132" s="5"/>
+      <c r="F132" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G132" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="H132" s="4" t="s">
+        <v>10</v>
+      </c>
       <c r="I132" t="s">
         <v>57</v>
       </c>
@@ -10712,9 +11087,16 @@
       <c r="E133">
         <v>5</v>
       </c>
-      <c r="F133" s="5"/>
-      <c r="G133" s="7"/>
-      <c r="H133" s="7"/>
+      <c r="F133" s="5">
+        <f t="shared" si="7"/>
+        <v>54</v>
+      </c>
+      <c r="G133" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="H133" s="5" t="s">
+        <v>49</v>
+      </c>
       <c r="I133" t="s">
         <v>57</v>
       </c>
@@ -10740,6 +11122,15 @@
       <c r="E135" s="4" t="s">
         <v>10</v>
       </c>
+      <c r="F135" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G135" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="H135" s="4" t="s">
+        <v>10</v>
+      </c>
       <c r="I135" t="s">
         <v>58</v>
       </c>
@@ -10821,7 +11212,7 @@
         <v>150</v>
       </c>
       <c r="F138" s="5">
-        <f t="shared" ref="F138:F144" si="11">(B138/E138)*100</f>
+        <f t="shared" ref="F138:F143" si="8">(B138/E138)*100</f>
         <v>45.6</v>
       </c>
       <c r="G138" s="5" t="s">
@@ -10851,7 +11242,7 @@
         <v>2.5</v>
       </c>
       <c r="F139" s="5">
-        <f t="shared" si="11"/>
+        <f t="shared" si="8"/>
         <v>40</v>
       </c>
       <c r="G139" s="5" t="s">
@@ -10881,7 +11272,7 @@
         <v>1.4</v>
       </c>
       <c r="F140" s="5">
-        <f t="shared" si="11"/>
+        <f t="shared" si="8"/>
         <v>78.571428571428584</v>
       </c>
       <c r="G140" s="5" t="s">
@@ -10911,7 +11302,7 @@
         <v>700</v>
       </c>
       <c r="F141" s="5">
-        <f t="shared" si="11"/>
+        <f t="shared" si="8"/>
         <v>61.428571428571431</v>
       </c>
       <c r="G141" s="5" t="s">
@@ -10941,7 +11332,7 @@
         <v>2000</v>
       </c>
       <c r="F142" s="5">
-        <f t="shared" si="11"/>
+        <f t="shared" si="8"/>
         <v>61.650000000000006</v>
       </c>
       <c r="G142" s="5" t="s">
@@ -10971,7 +11362,7 @@
         <v>375</v>
       </c>
       <c r="F143" s="5">
-        <f t="shared" si="11"/>
+        <f t="shared" si="8"/>
         <v>17.866666666666667</v>
       </c>
       <c r="G143" s="5" t="s">
@@ -11000,12 +11391,15 @@
       <c r="E144">
         <v>800</v>
       </c>
-      <c r="F144" s="5" t="e">
-        <f t="shared" si="11"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="G144" s="5"/>
-      <c r="H144" s="5"/>
+      <c r="F144" t="s">
+        <v>10</v>
+      </c>
+      <c r="G144" t="s">
+        <v>10</v>
+      </c>
+      <c r="H144" t="s">
+        <v>10</v>
+      </c>
       <c r="I144" t="s">
         <v>58</v>
       </c>
@@ -11026,9 +11420,15 @@
       <c r="E145">
         <v>5</v>
       </c>
-      <c r="F145" s="5"/>
-      <c r="G145" s="7"/>
-      <c r="H145" s="7"/>
+      <c r="F145" t="s">
+        <v>10</v>
+      </c>
+      <c r="G145" t="s">
+        <v>10</v>
+      </c>
+      <c r="H145" t="s">
+        <v>10</v>
+      </c>
       <c r="I145" t="s">
         <v>58</v>
       </c>
@@ -11054,6 +11454,15 @@
       <c r="E147" s="4" t="s">
         <v>10</v>
       </c>
+      <c r="F147" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G147" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="H147" s="4" t="s">
+        <v>10</v>
+      </c>
       <c r="I147" t="s">
         <v>59</v>
       </c>
@@ -11135,7 +11544,7 @@
         <v>150</v>
       </c>
       <c r="F150" s="5">
-        <f t="shared" ref="F150:F156" si="12">(B150/E150)*100</f>
+        <f t="shared" ref="F150:F155" si="9">(B150/E150)*100</f>
         <v>45.333333333333329</v>
       </c>
       <c r="G150" s="5" t="s">
@@ -11165,7 +11574,7 @@
         <v>2.5</v>
       </c>
       <c r="F151" s="5">
-        <f t="shared" si="12"/>
+        <f t="shared" si="9"/>
         <v>40</v>
       </c>
       <c r="G151" s="5" t="s">
@@ -11195,7 +11604,7 @@
         <v>1.4</v>
       </c>
       <c r="F152" s="5">
-        <f t="shared" si="12"/>
+        <f t="shared" si="9"/>
         <v>62.857142857142868</v>
       </c>
       <c r="G152" s="5" t="s">
@@ -11225,7 +11634,7 @@
         <v>700</v>
       </c>
       <c r="F153" s="5">
-        <f t="shared" si="12"/>
+        <f t="shared" si="9"/>
         <v>56.999999999999993</v>
       </c>
       <c r="G153" s="5" t="s">
@@ -11255,7 +11664,7 @@
         <v>2000</v>
       </c>
       <c r="F154" s="5">
-        <f t="shared" si="12"/>
+        <f t="shared" si="9"/>
         <v>63.65</v>
       </c>
       <c r="G154" s="5" t="s">
@@ -11285,7 +11694,7 @@
         <v>375</v>
       </c>
       <c r="F155" s="5">
-        <f t="shared" si="12"/>
+        <f t="shared" si="9"/>
         <v>18.933333333333334</v>
       </c>
       <c r="G155" s="5" t="s">
@@ -11314,12 +11723,15 @@
       <c r="E156">
         <v>800</v>
       </c>
-      <c r="F156" s="5" t="e">
-        <f t="shared" si="12"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="G156" s="5"/>
-      <c r="H156" s="5"/>
+      <c r="F156" t="s">
+        <v>10</v>
+      </c>
+      <c r="G156" t="s">
+        <v>10</v>
+      </c>
+      <c r="H156" t="s">
+        <v>10</v>
+      </c>
       <c r="I156" t="s">
         <v>59</v>
       </c>
@@ -11340,9 +11752,15 @@
       <c r="E157">
         <v>5</v>
       </c>
-      <c r="F157" s="5"/>
-      <c r="G157" s="7"/>
-      <c r="H157" s="7"/>
+      <c r="F157" t="s">
+        <v>10</v>
+      </c>
+      <c r="G157" t="s">
+        <v>10</v>
+      </c>
+      <c r="H157" t="s">
+        <v>10</v>
+      </c>
       <c r="I157" t="s">
         <v>59</v>
       </c>
@@ -11365,6 +11783,15 @@
       <c r="E159" s="4" t="s">
         <v>10</v>
       </c>
+      <c r="F159" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G159" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="H159" s="4" t="s">
+        <v>10</v>
+      </c>
       <c r="I159" t="s">
         <v>60</v>
       </c>
@@ -11437,7 +11864,7 @@
         <v>150</v>
       </c>
       <c r="F162" s="5">
-        <f t="shared" ref="F162:F168" si="13">(B162/E162)*100</f>
+        <f t="shared" ref="F162:F167" si="10">(B162/E162)*100</f>
         <v>0</v>
       </c>
       <c r="G162" s="5" t="s">
@@ -11464,7 +11891,7 @@
         <v>2.5</v>
       </c>
       <c r="F163" s="5">
-        <f t="shared" si="13"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="G163" s="5" t="s">
@@ -11491,7 +11918,7 @@
         <v>1.4</v>
       </c>
       <c r="F164" s="5">
-        <f t="shared" si="13"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="G164" s="5" t="s">
@@ -11518,7 +11945,7 @@
         <v>700</v>
       </c>
       <c r="F165" s="5">
-        <f t="shared" si="13"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="G165" s="5" t="s">
@@ -11545,7 +11972,7 @@
         <v>2000</v>
       </c>
       <c r="F166" s="5">
-        <f t="shared" si="13"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="G166" s="5" t="s">
@@ -11572,7 +11999,7 @@
         <v>375</v>
       </c>
       <c r="F167" s="5">
-        <f t="shared" si="13"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="G167" s="5" t="s">
@@ -11601,12 +12028,15 @@
       <c r="E168">
         <v>800</v>
       </c>
-      <c r="F168" s="5" t="e">
-        <f t="shared" si="13"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="G168" s="5"/>
-      <c r="H168" s="5"/>
+      <c r="F168" t="s">
+        <v>10</v>
+      </c>
+      <c r="G168" t="s">
+        <v>10</v>
+      </c>
+      <c r="H168" t="s">
+        <v>10</v>
+      </c>
       <c r="I168" t="s">
         <v>60</v>
       </c>
@@ -11627,9 +12057,15 @@
       <c r="E169">
         <v>5</v>
       </c>
-      <c r="F169" s="5"/>
-      <c r="G169" s="7"/>
-      <c r="H169" s="7"/>
+      <c r="F169" t="s">
+        <v>10</v>
+      </c>
+      <c r="G169" t="s">
+        <v>10</v>
+      </c>
+      <c r="H169" t="s">
+        <v>10</v>
+      </c>
       <c r="I169" t="s">
         <v>60</v>
       </c>
@@ -11655,6 +12091,15 @@
       <c r="E171" s="4" t="s">
         <v>10</v>
       </c>
+      <c r="F171" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G171" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="H171" s="4" t="s">
+        <v>10</v>
+      </c>
       <c r="I171" t="s">
         <v>61</v>
       </c>
@@ -11736,7 +12181,7 @@
         <v>150</v>
       </c>
       <c r="F174" s="5">
-        <f t="shared" ref="F174:F180" si="14">(B174/E174)*100</f>
+        <f t="shared" ref="F174:F180" si="11">(B174/E174)*100</f>
         <v>45.333333333333329</v>
       </c>
       <c r="G174" s="5" t="s">
@@ -11766,7 +12211,7 @@
         <v>2.5</v>
       </c>
       <c r="F175" s="5">
-        <f t="shared" si="14"/>
+        <f t="shared" si="11"/>
         <v>40</v>
       </c>
       <c r="G175" s="5" t="s">
@@ -11796,7 +12241,7 @@
         <v>1.4</v>
       </c>
       <c r="F176" s="5">
-        <f t="shared" si="14"/>
+        <f t="shared" si="11"/>
         <v>80.000000000000014</v>
       </c>
       <c r="G176" s="5" t="s">
@@ -11826,7 +12271,7 @@
         <v>700</v>
       </c>
       <c r="F177" s="5">
-        <f t="shared" si="14"/>
+        <f t="shared" si="11"/>
         <v>61.428571428571431</v>
       </c>
       <c r="G177" s="5" t="s">
@@ -11856,7 +12301,7 @@
         <v>2000</v>
       </c>
       <c r="F178" s="5">
-        <f t="shared" si="14"/>
+        <f t="shared" si="11"/>
         <v>61.650000000000006</v>
       </c>
       <c r="G178" s="5" t="s">
@@ -11886,7 +12331,7 @@
         <v>375</v>
       </c>
       <c r="F179" s="5">
-        <f t="shared" si="14"/>
+        <f t="shared" si="11"/>
         <v>17.866666666666667</v>
       </c>
       <c r="G179" s="5" t="s">
@@ -11916,7 +12361,7 @@
         <v>800</v>
       </c>
       <c r="F180" s="7">
-        <f t="shared" si="14"/>
+        <f t="shared" si="11"/>
         <v>9.25</v>
       </c>
       <c r="G180" s="7" t="s">
@@ -11979,6 +12424,15 @@
       <c r="E183" s="4" t="s">
         <v>10</v>
       </c>
+      <c r="F183" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G183" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="H183" s="4" t="s">
+        <v>10</v>
+      </c>
       <c r="I183" t="s">
         <v>62</v>
       </c>
@@ -12060,7 +12514,7 @@
         <v>150</v>
       </c>
       <c r="F186" s="5">
-        <f t="shared" ref="F186:F192" si="15">(B186/E186)*100</f>
+        <f t="shared" ref="F186:F192" si="12">(B186/E186)*100</f>
         <v>45.333333333333329</v>
       </c>
       <c r="G186" s="5" t="s">
@@ -12090,7 +12544,7 @@
         <v>2.5</v>
       </c>
       <c r="F187" s="5">
-        <f t="shared" si="15"/>
+        <f t="shared" si="12"/>
         <v>40</v>
       </c>
       <c r="G187" s="5" t="s">
@@ -12120,7 +12574,7 @@
         <v>1.4</v>
       </c>
       <c r="F188" s="5">
-        <f t="shared" si="15"/>
+        <f t="shared" si="12"/>
         <v>62.857142857142868</v>
       </c>
       <c r="G188" s="5" t="s">
@@ -12150,7 +12604,7 @@
         <v>700</v>
       </c>
       <c r="F189" s="5">
-        <f t="shared" si="15"/>
+        <f t="shared" si="12"/>
         <v>56.999999999999993</v>
       </c>
       <c r="G189" s="5" t="s">
@@ -12180,7 +12634,7 @@
         <v>2000</v>
       </c>
       <c r="F190" s="5">
-        <f t="shared" si="15"/>
+        <f t="shared" si="12"/>
         <v>63.65</v>
       </c>
       <c r="G190" s="5" t="s">
@@ -12210,7 +12664,7 @@
         <v>375</v>
       </c>
       <c r="F191" s="5">
-        <f t="shared" si="15"/>
+        <f t="shared" si="12"/>
         <v>18.933333333333334</v>
       </c>
       <c r="G191" s="5" t="s">
@@ -12240,7 +12694,7 @@
         <v>800</v>
       </c>
       <c r="F192" s="7">
-        <f t="shared" si="15"/>
+        <f t="shared" si="12"/>
         <v>4.75</v>
       </c>
       <c r="G192" s="7" t="s">
@@ -12345,6 +12799,15 @@
       <c r="E3" s="4" t="s">
         <v>10</v>
       </c>
+      <c r="F3" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G3" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="H3" s="4" t="s">
+        <v>10</v>
+      </c>
       <c r="I3" t="s">
         <v>63</v>
       </c>
@@ -12670,6 +13133,15 @@
       <c r="E15" s="4" t="s">
         <v>10</v>
       </c>
+      <c r="F15" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G15" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="H15" s="4" t="s">
+        <v>10</v>
+      </c>
       <c r="I15" t="s">
         <v>64</v>
       </c>
@@ -12995,6 +13467,15 @@
       <c r="E27" s="4" t="s">
         <v>10</v>
       </c>
+      <c r="F27" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G27" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="H27" s="4" t="s">
+        <v>10</v>
+      </c>
       <c r="I27" t="s">
         <v>65</v>
       </c>
@@ -13320,6 +13801,15 @@
       <c r="E39" s="4" t="s">
         <v>10</v>
       </c>
+      <c r="F39" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G39" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="H39" s="4" t="s">
+        <v>10</v>
+      </c>
       <c r="I39" t="s">
         <v>66</v>
       </c>
@@ -13645,6 +14135,15 @@
       <c r="E51" s="4" t="s">
         <v>10</v>
       </c>
+      <c r="F51" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G51" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="H51" s="4" t="s">
+        <v>10</v>
+      </c>
       <c r="I51" t="s">
         <v>67</v>
       </c>
@@ -13695,15 +14194,14 @@
       <c r="E53">
         <v>800</v>
       </c>
-      <c r="F53" s="5" t="e">
-        <f>(B53/E53)*100</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="G53" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="H53" s="7" t="s">
-        <v>23</v>
+      <c r="F53" t="s">
+        <v>10</v>
+      </c>
+      <c r="G53" t="s">
+        <v>10</v>
+      </c>
+      <c r="H53" t="s">
+        <v>10</v>
       </c>
       <c r="I53" t="s">
         <v>67</v>
@@ -13725,15 +14223,14 @@
       <c r="E54">
         <v>150</v>
       </c>
-      <c r="F54" s="7" t="e">
-        <f t="shared" ref="F54:F60" si="4">(B54/E54)*100</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="G54" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="H54" s="7" t="s">
-        <v>23</v>
+      <c r="F54" t="s">
+        <v>10</v>
+      </c>
+      <c r="G54" t="s">
+        <v>10</v>
+      </c>
+      <c r="H54" t="s">
+        <v>10</v>
       </c>
       <c r="I54" t="s">
         <v>67</v>
@@ -13755,15 +14252,14 @@
       <c r="E55">
         <v>2.5</v>
       </c>
-      <c r="F55" s="5" t="e">
-        <f t="shared" si="4"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="G55" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="H55" s="7" t="s">
-        <v>23</v>
+      <c r="F55" t="s">
+        <v>10</v>
+      </c>
+      <c r="G55" t="s">
+        <v>10</v>
+      </c>
+      <c r="H55" t="s">
+        <v>10</v>
       </c>
       <c r="I55" t="s">
         <v>67</v>
@@ -13785,15 +14281,14 @@
       <c r="E56">
         <v>1.4</v>
       </c>
-      <c r="F56" s="7" t="e">
-        <f t="shared" si="4"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="G56" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="H56" s="7" t="s">
-        <v>23</v>
+      <c r="F56" t="s">
+        <v>10</v>
+      </c>
+      <c r="G56" t="s">
+        <v>10</v>
+      </c>
+      <c r="H56" t="s">
+        <v>10</v>
       </c>
       <c r="I56" t="s">
         <v>67</v>
@@ -13815,15 +14310,14 @@
       <c r="E57">
         <v>700</v>
       </c>
-      <c r="F57" s="5" t="e">
-        <f t="shared" si="4"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="G57" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="H57" s="7" t="s">
-        <v>23</v>
+      <c r="F57" t="s">
+        <v>10</v>
+      </c>
+      <c r="G57" t="s">
+        <v>10</v>
+      </c>
+      <c r="H57" t="s">
+        <v>10</v>
       </c>
       <c r="I57" t="s">
         <v>67</v>
@@ -13845,15 +14339,14 @@
       <c r="E58">
         <v>2000</v>
       </c>
-      <c r="F58" s="7" t="e">
-        <f t="shared" si="4"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="G58" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="H58" s="7" t="s">
-        <v>23</v>
+      <c r="F58" t="s">
+        <v>10</v>
+      </c>
+      <c r="G58" t="s">
+        <v>10</v>
+      </c>
+      <c r="H58" t="s">
+        <v>10</v>
       </c>
       <c r="I58" t="s">
         <v>67</v>
@@ -13875,15 +14368,14 @@
       <c r="E59">
         <v>375</v>
       </c>
-      <c r="F59" s="7" t="e">
-        <f t="shared" si="4"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="G59" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="H59" s="7" t="s">
-        <v>23</v>
+      <c r="F59" t="s">
+        <v>10</v>
+      </c>
+      <c r="G59" t="s">
+        <v>10</v>
+      </c>
+      <c r="H59" t="s">
+        <v>10</v>
       </c>
       <c r="I59" t="s">
         <v>67</v>
@@ -13905,15 +14397,14 @@
       <c r="E60">
         <v>800</v>
       </c>
-      <c r="F60" s="7" t="e">
-        <f t="shared" si="4"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="G60" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="H60" s="7" t="s">
-        <v>23</v>
+      <c r="F60" t="s">
+        <v>10</v>
+      </c>
+      <c r="G60" t="s">
+        <v>10</v>
+      </c>
+      <c r="H60" t="s">
+        <v>10</v>
       </c>
       <c r="I60" t="s">
         <v>67</v>
@@ -13935,12 +14426,14 @@
       <c r="E61">
         <v>5</v>
       </c>
-      <c r="F61" s="5"/>
-      <c r="G61" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="H61" s="7" t="s">
-        <v>23</v>
+      <c r="F61" t="s">
+        <v>10</v>
+      </c>
+      <c r="G61" t="s">
+        <v>10</v>
+      </c>
+      <c r="H61" t="s">
+        <v>10</v>
       </c>
       <c r="I61" t="s">
         <v>67</v>
@@ -13967,6 +14460,15 @@
       <c r="E63" s="4" t="s">
         <v>10</v>
       </c>
+      <c r="F63" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G63" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="H63" s="4" t="s">
+        <v>10</v>
+      </c>
       <c r="I63" t="s">
         <v>68</v>
       </c>
@@ -14047,15 +14549,14 @@
       <c r="E66">
         <v>150</v>
       </c>
-      <c r="F66" s="7" t="e">
-        <f t="shared" ref="F66:F72" si="5">(B66/E66)*100</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="G66" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="H66" s="7" t="s">
-        <v>23</v>
+      <c r="F66" t="s">
+        <v>10</v>
+      </c>
+      <c r="G66" t="s">
+        <v>10</v>
+      </c>
+      <c r="H66" t="s">
+        <v>10</v>
       </c>
       <c r="I66" t="s">
         <v>68</v>
@@ -14078,7 +14579,7 @@
         <v>2.5</v>
       </c>
       <c r="F67" s="5">
-        <f t="shared" si="5"/>
+        <f t="shared" ref="F67" si="4">(B67/E67)*100</f>
         <v>20</v>
       </c>
       <c r="G67" s="5" t="s">
@@ -14107,15 +14608,14 @@
       <c r="E68">
         <v>1.4</v>
       </c>
-      <c r="F68" s="7" t="e">
-        <f t="shared" si="5"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="G68" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="H68" s="7" t="s">
-        <v>23</v>
+      <c r="F68" t="s">
+        <v>10</v>
+      </c>
+      <c r="G68" t="s">
+        <v>10</v>
+      </c>
+      <c r="H68" t="s">
+        <v>10</v>
       </c>
       <c r="I68" t="s">
         <v>68</v>
@@ -14137,15 +14637,14 @@
       <c r="E69">
         <v>700</v>
       </c>
-      <c r="F69" s="5" t="e">
-        <f t="shared" si="5"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="G69" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="H69" s="7" t="s">
-        <v>23</v>
+      <c r="F69" t="s">
+        <v>10</v>
+      </c>
+      <c r="G69" t="s">
+        <v>10</v>
+      </c>
+      <c r="H69" t="s">
+        <v>10</v>
       </c>
       <c r="I69" t="s">
         <v>68</v>
@@ -14167,15 +14666,14 @@
       <c r="E70">
         <v>2000</v>
       </c>
-      <c r="F70" s="7" t="e">
-        <f t="shared" si="5"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="G70" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="H70" s="7" t="s">
-        <v>23</v>
+      <c r="F70" t="s">
+        <v>10</v>
+      </c>
+      <c r="G70" t="s">
+        <v>10</v>
+      </c>
+      <c r="H70" t="s">
+        <v>10</v>
       </c>
       <c r="I70" t="s">
         <v>68</v>
@@ -14197,15 +14695,14 @@
       <c r="E71">
         <v>375</v>
       </c>
-      <c r="F71" s="7" t="e">
-        <f t="shared" si="5"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="G71" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="H71" s="7" t="s">
-        <v>23</v>
+      <c r="F71" t="s">
+        <v>10</v>
+      </c>
+      <c r="G71" t="s">
+        <v>10</v>
+      </c>
+      <c r="H71" t="s">
+        <v>10</v>
       </c>
       <c r="I71" t="s">
         <v>68</v>
@@ -14227,15 +14724,14 @@
       <c r="E72">
         <v>800</v>
       </c>
-      <c r="F72" s="7" t="e">
-        <f t="shared" si="5"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="G72" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="H72" s="7" t="s">
-        <v>23</v>
+      <c r="F72" t="s">
+        <v>10</v>
+      </c>
+      <c r="G72" t="s">
+        <v>10</v>
+      </c>
+      <c r="H72" t="s">
+        <v>10</v>
       </c>
       <c r="I72" t="s">
         <v>68</v>
@@ -14257,12 +14753,14 @@
       <c r="E73">
         <v>5</v>
       </c>
-      <c r="F73" s="5"/>
-      <c r="G73" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="H73" s="7" t="s">
-        <v>23</v>
+      <c r="F73" t="s">
+        <v>10</v>
+      </c>
+      <c r="G73" t="s">
+        <v>10</v>
+      </c>
+      <c r="H73" t="s">
+        <v>10</v>
       </c>
       <c r="I73" t="s">
         <v>68</v>
@@ -14289,6 +14787,15 @@
       <c r="E75" s="4" t="s">
         <v>10</v>
       </c>
+      <c r="F75" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G75" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="H75" s="4" t="s">
+        <v>10</v>
+      </c>
       <c r="I75" t="s">
         <v>69</v>
       </c>
@@ -14369,15 +14876,14 @@
       <c r="E78">
         <v>150</v>
       </c>
-      <c r="F78" s="7" t="e">
-        <f t="shared" ref="F78:F84" si="6">(B78/E78)*100</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="G78" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="H78" s="7" t="s">
-        <v>23</v>
+      <c r="F78" t="s">
+        <v>10</v>
+      </c>
+      <c r="G78" t="s">
+        <v>10</v>
+      </c>
+      <c r="H78" t="s">
+        <v>10</v>
       </c>
       <c r="I78" t="s">
         <v>69</v>
@@ -14400,7 +14906,7 @@
         <v>2.5</v>
       </c>
       <c r="F79" s="5">
-        <f t="shared" si="6"/>
+        <f t="shared" ref="F79" si="5">(B79/E79)*100</f>
         <v>16</v>
       </c>
       <c r="G79" s="5" t="s">
@@ -14429,15 +14935,14 @@
       <c r="E80">
         <v>1.4</v>
       </c>
-      <c r="F80" s="7" t="e">
-        <f t="shared" si="6"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="G80" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="H80" s="7" t="s">
-        <v>23</v>
+      <c r="F80" t="s">
+        <v>10</v>
+      </c>
+      <c r="G80" t="s">
+        <v>10</v>
+      </c>
+      <c r="H80" t="s">
+        <v>10</v>
       </c>
       <c r="I80" t="s">
         <v>69</v>
@@ -14459,15 +14964,14 @@
       <c r="E81">
         <v>700</v>
       </c>
-      <c r="F81" s="5" t="e">
-        <f t="shared" si="6"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="G81" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="H81" s="7" t="s">
-        <v>23</v>
+      <c r="F81" t="s">
+        <v>10</v>
+      </c>
+      <c r="G81" t="s">
+        <v>10</v>
+      </c>
+      <c r="H81" t="s">
+        <v>10</v>
       </c>
       <c r="I81" t="s">
         <v>69</v>
@@ -14489,15 +14993,14 @@
       <c r="E82">
         <v>2000</v>
       </c>
-      <c r="F82" s="7" t="e">
-        <f t="shared" si="6"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="G82" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="H82" s="7" t="s">
-        <v>23</v>
+      <c r="F82" t="s">
+        <v>10</v>
+      </c>
+      <c r="G82" t="s">
+        <v>10</v>
+      </c>
+      <c r="H82" t="s">
+        <v>10</v>
       </c>
       <c r="I82" t="s">
         <v>69</v>
@@ -14519,15 +15022,14 @@
       <c r="E83">
         <v>375</v>
       </c>
-      <c r="F83" s="7" t="e">
-        <f t="shared" si="6"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="G83" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="H83" s="7" t="s">
-        <v>23</v>
+      <c r="F83" t="s">
+        <v>10</v>
+      </c>
+      <c r="G83" t="s">
+        <v>10</v>
+      </c>
+      <c r="H83" t="s">
+        <v>10</v>
       </c>
       <c r="I83" t="s">
         <v>69</v>
@@ -14549,15 +15051,14 @@
       <c r="E84">
         <v>800</v>
       </c>
-      <c r="F84" s="7" t="e">
-        <f t="shared" si="6"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="G84" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="H84" s="7" t="s">
-        <v>23</v>
+      <c r="F84" t="s">
+        <v>10</v>
+      </c>
+      <c r="G84" t="s">
+        <v>10</v>
+      </c>
+      <c r="H84" t="s">
+        <v>10</v>
       </c>
       <c r="I84" t="s">
         <v>69</v>
@@ -14579,12 +15080,14 @@
       <c r="E85">
         <v>5</v>
       </c>
-      <c r="F85" s="5"/>
-      <c r="G85" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="H85" s="7" t="s">
-        <v>23</v>
+      <c r="F85" t="s">
+        <v>10</v>
+      </c>
+      <c r="G85" t="s">
+        <v>10</v>
+      </c>
+      <c r="H85" t="s">
+        <v>10</v>
       </c>
       <c r="I85" t="s">
         <v>69</v>
@@ -14611,6 +15114,15 @@
       <c r="E87" s="4" t="s">
         <v>10</v>
       </c>
+      <c r="F87" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G87" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="H87" s="4" t="s">
+        <v>10</v>
+      </c>
       <c r="I87" t="s">
         <v>70</v>
       </c>
@@ -14691,15 +15203,14 @@
       <c r="E90">
         <v>150</v>
       </c>
-      <c r="F90" s="7" t="e">
-        <f t="shared" ref="F90:F96" si="7">(B90/E90)*100</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="G90" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="H90" s="7" t="s">
-        <v>23</v>
+      <c r="F90" t="s">
+        <v>10</v>
+      </c>
+      <c r="G90" t="s">
+        <v>10</v>
+      </c>
+      <c r="H90" t="s">
+        <v>10</v>
       </c>
       <c r="I90" t="s">
         <v>70</v>
@@ -14722,7 +15233,7 @@
         <v>2.5</v>
       </c>
       <c r="F91" s="5">
-        <f t="shared" si="7"/>
+        <f t="shared" ref="F91:F93" si="6">(B91/E91)*100</f>
         <v>22.799999999999997</v>
       </c>
       <c r="G91" s="5" t="s">
@@ -14751,15 +15262,14 @@
       <c r="E92">
         <v>1.4</v>
       </c>
-      <c r="F92" s="7" t="e">
-        <f t="shared" si="7"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="G92" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="H92" s="7" t="s">
-        <v>23</v>
+      <c r="F92" t="s">
+        <v>10</v>
+      </c>
+      <c r="G92" t="s">
+        <v>10</v>
+      </c>
+      <c r="H92" t="s">
+        <v>10</v>
       </c>
       <c r="I92" t="s">
         <v>70</v>
@@ -14782,7 +15292,7 @@
         <v>700</v>
       </c>
       <c r="F93" s="5">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>16.714285714285715</v>
       </c>
       <c r="G93" s="5" t="s">
@@ -14811,15 +15321,14 @@
       <c r="E94">
         <v>2000</v>
       </c>
-      <c r="F94" s="7" t="e">
-        <f t="shared" si="7"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="G94" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="H94" s="7" t="s">
-        <v>23</v>
+      <c r="F94" t="s">
+        <v>10</v>
+      </c>
+      <c r="G94" t="s">
+        <v>10</v>
+      </c>
+      <c r="H94" t="s">
+        <v>10</v>
       </c>
       <c r="I94" t="s">
         <v>70</v>
@@ -14841,15 +15350,14 @@
       <c r="E95">
         <v>375</v>
       </c>
-      <c r="F95" s="7" t="e">
-        <f t="shared" si="7"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="G95" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="H95" s="7" t="s">
-        <v>23</v>
+      <c r="F95" t="s">
+        <v>10</v>
+      </c>
+      <c r="G95" t="s">
+        <v>10</v>
+      </c>
+      <c r="H95" t="s">
+        <v>10</v>
       </c>
       <c r="I95" t="s">
         <v>70</v>
@@ -14871,15 +15379,14 @@
       <c r="E96">
         <v>800</v>
       </c>
-      <c r="F96" s="7" t="e">
-        <f t="shared" si="7"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="G96" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="H96" s="7" t="s">
-        <v>23</v>
+      <c r="F96" t="s">
+        <v>10</v>
+      </c>
+      <c r="G96" t="s">
+        <v>10</v>
+      </c>
+      <c r="H96" t="s">
+        <v>10</v>
       </c>
       <c r="I96" t="s">
         <v>70</v>
@@ -14901,12 +15408,14 @@
       <c r="E97">
         <v>5</v>
       </c>
-      <c r="F97" s="5"/>
-      <c r="G97" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="H97" s="7" t="s">
-        <v>23</v>
+      <c r="F97" t="s">
+        <v>10</v>
+      </c>
+      <c r="G97" t="s">
+        <v>10</v>
+      </c>
+      <c r="H97" t="s">
+        <v>10</v>
       </c>
       <c r="I97" t="s">
         <v>70</v>
@@ -14933,6 +15442,15 @@
       <c r="E99" s="4" t="s">
         <v>10</v>
       </c>
+      <c r="F99" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G99" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="H99" s="4" t="s">
+        <v>10</v>
+      </c>
       <c r="I99" t="s">
         <v>71</v>
       </c>
@@ -14983,9 +15501,8 @@
       <c r="E101">
         <v>800</v>
       </c>
-      <c r="F101" s="5" t="e">
-        <f>(B101/E101)*100</f>
-        <v>#VALUE!</v>
+      <c r="F101" t="s">
+        <v>10</v>
       </c>
       <c r="G101" s="5" t="s">
         <v>20</v>
@@ -15013,9 +15530,8 @@
       <c r="E102">
         <v>150</v>
       </c>
-      <c r="F102" s="7" t="e">
-        <f t="shared" ref="F102:F108" si="8">(B102/E102)*100</f>
-        <v>#VALUE!</v>
+      <c r="F102" t="s">
+        <v>10</v>
       </c>
       <c r="G102" s="7" t="s">
         <v>23</v>
@@ -15044,7 +15560,7 @@
         <v>2.5</v>
       </c>
       <c r="F103" s="5">
-        <f t="shared" si="8"/>
+        <f t="shared" ref="F103" si="7">(B103/E103)*100</f>
         <v>16</v>
       </c>
       <c r="G103" s="5" t="s">
@@ -15073,15 +15589,14 @@
       <c r="E104">
         <v>1.4</v>
       </c>
-      <c r="F104" s="7" t="e">
-        <f t="shared" si="8"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="G104" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="H104" s="7" t="s">
-        <v>23</v>
+      <c r="F104" t="s">
+        <v>10</v>
+      </c>
+      <c r="G104" t="s">
+        <v>10</v>
+      </c>
+      <c r="H104" t="s">
+        <v>10</v>
       </c>
       <c r="I104" t="s">
         <v>71</v>
@@ -15103,15 +15618,14 @@
       <c r="E105">
         <v>700</v>
       </c>
-      <c r="F105" s="5" t="e">
-        <f t="shared" si="8"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="G105" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="H105" s="7" t="s">
-        <v>23</v>
+      <c r="F105" t="s">
+        <v>10</v>
+      </c>
+      <c r="G105" t="s">
+        <v>10</v>
+      </c>
+      <c r="H105" t="s">
+        <v>10</v>
       </c>
       <c r="I105" t="s">
         <v>71</v>
@@ -15133,15 +15647,14 @@
       <c r="E106">
         <v>2000</v>
       </c>
-      <c r="F106" s="7" t="e">
-        <f t="shared" si="8"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="G106" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="H106" s="7" t="s">
-        <v>23</v>
+      <c r="F106" t="s">
+        <v>10</v>
+      </c>
+      <c r="G106" t="s">
+        <v>10</v>
+      </c>
+      <c r="H106" t="s">
+        <v>10</v>
       </c>
       <c r="I106" t="s">
         <v>71</v>
@@ -15163,15 +15676,14 @@
       <c r="E107">
         <v>375</v>
       </c>
-      <c r="F107" s="7" t="e">
-        <f t="shared" si="8"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="G107" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="H107" s="7" t="s">
-        <v>23</v>
+      <c r="F107" t="s">
+        <v>10</v>
+      </c>
+      <c r="G107" t="s">
+        <v>10</v>
+      </c>
+      <c r="H107" t="s">
+        <v>10</v>
       </c>
       <c r="I107" t="s">
         <v>71</v>
@@ -15193,15 +15705,14 @@
       <c r="E108">
         <v>800</v>
       </c>
-      <c r="F108" s="7" t="e">
-        <f t="shared" si="8"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="G108" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="H108" s="7" t="s">
-        <v>23</v>
+      <c r="F108" t="s">
+        <v>10</v>
+      </c>
+      <c r="G108" t="s">
+        <v>10</v>
+      </c>
+      <c r="H108" t="s">
+        <v>10</v>
       </c>
       <c r="I108" t="s">
         <v>71</v>
@@ -15223,12 +15734,14 @@
       <c r="E109">
         <v>5</v>
       </c>
-      <c r="F109" s="5"/>
-      <c r="G109" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="H109" s="7" t="s">
-        <v>23</v>
+      <c r="F109" t="s">
+        <v>10</v>
+      </c>
+      <c r="G109" t="s">
+        <v>10</v>
+      </c>
+      <c r="H109" t="s">
+        <v>10</v>
       </c>
       <c r="I109" t="s">
         <v>71</v>
@@ -15255,6 +15768,15 @@
       <c r="E111" s="4" t="s">
         <v>10</v>
       </c>
+      <c r="F111" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G111" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="H111" s="4" t="s">
+        <v>10</v>
+      </c>
       <c r="I111" t="s">
         <v>72</v>
       </c>
@@ -15335,15 +15857,14 @@
       <c r="E114">
         <v>150</v>
       </c>
-      <c r="F114" s="7" t="e">
-        <f t="shared" ref="F114:F120" si="9">(B114/E114)*100</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="G114" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="H114" s="7" t="s">
-        <v>23</v>
+      <c r="F114" t="s">
+        <v>10</v>
+      </c>
+      <c r="G114" t="s">
+        <v>10</v>
+      </c>
+      <c r="H114" t="s">
+        <v>10</v>
       </c>
       <c r="I114" t="s">
         <v>72</v>
@@ -15366,7 +15887,7 @@
         <v>2.5</v>
       </c>
       <c r="F115" s="5">
-        <f t="shared" si="9"/>
+        <f t="shared" ref="F115:F117" si="8">(B115/E115)*100</f>
         <v>22.799999999999997</v>
       </c>
       <c r="G115" s="5" t="s">
@@ -15395,15 +15916,14 @@
       <c r="E116">
         <v>1.4</v>
       </c>
-      <c r="F116" s="7" t="e">
-        <f t="shared" si="9"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="G116" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="H116" s="7" t="s">
-        <v>23</v>
+      <c r="F116" t="s">
+        <v>10</v>
+      </c>
+      <c r="G116" t="s">
+        <v>10</v>
+      </c>
+      <c r="H116" t="s">
+        <v>10</v>
       </c>
       <c r="I116" t="s">
         <v>72</v>
@@ -15426,7 +15946,7 @@
         <v>700</v>
       </c>
       <c r="F117" s="5">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>16.714285714285715</v>
       </c>
       <c r="G117" s="5" t="s">
@@ -15455,15 +15975,14 @@
       <c r="E118">
         <v>2000</v>
       </c>
-      <c r="F118" s="7" t="e">
-        <f t="shared" si="9"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="G118" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="H118" s="7" t="s">
-        <v>23</v>
+      <c r="F118" t="s">
+        <v>10</v>
+      </c>
+      <c r="G118" t="s">
+        <v>10</v>
+      </c>
+      <c r="H118" t="s">
+        <v>10</v>
       </c>
       <c r="I118" t="s">
         <v>72</v>
@@ -15485,15 +16004,14 @@
       <c r="E119">
         <v>375</v>
       </c>
-      <c r="F119" s="7" t="e">
-        <f t="shared" si="9"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="G119" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="H119" s="7" t="s">
-        <v>23</v>
+      <c r="F119" t="s">
+        <v>10</v>
+      </c>
+      <c r="G119" t="s">
+        <v>10</v>
+      </c>
+      <c r="H119" t="s">
+        <v>10</v>
       </c>
       <c r="I119" t="s">
         <v>72</v>
@@ -15515,15 +16033,14 @@
       <c r="E120">
         <v>800</v>
       </c>
-      <c r="F120" s="7" t="e">
-        <f t="shared" si="9"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="G120" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="H120" s="7" t="s">
-        <v>23</v>
+      <c r="F120" t="s">
+        <v>10</v>
+      </c>
+      <c r="G120" t="s">
+        <v>10</v>
+      </c>
+      <c r="H120" t="s">
+        <v>10</v>
       </c>
       <c r="I120" t="s">
         <v>72</v>
@@ -15545,12 +16062,14 @@
       <c r="E121">
         <v>5</v>
       </c>
-      <c r="F121" s="5"/>
-      <c r="G121" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="H121" s="7" t="s">
-        <v>23</v>
+      <c r="F121" t="s">
+        <v>10</v>
+      </c>
+      <c r="G121" t="s">
+        <v>10</v>
+      </c>
+      <c r="H121" t="s">
+        <v>10</v>
       </c>
       <c r="I121" t="s">
         <v>72</v>
@@ -15577,6 +16096,15 @@
       <c r="E123" s="4" t="s">
         <v>10</v>
       </c>
+      <c r="F123" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G123" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="H123" s="4" t="s">
+        <v>10</v>
+      </c>
       <c r="I123" t="s">
         <v>73</v>
       </c>
@@ -15657,15 +16185,14 @@
       <c r="E126">
         <v>150</v>
       </c>
-      <c r="F126" s="7" t="e">
-        <f t="shared" ref="F126:F133" si="10">(B126/E126)*100</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="G126" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="H126" s="7" t="s">
-        <v>23</v>
+      <c r="F126" t="s">
+        <v>10</v>
+      </c>
+      <c r="G126" t="s">
+        <v>10</v>
+      </c>
+      <c r="H126" t="s">
+        <v>10</v>
       </c>
       <c r="I126" t="s">
         <v>73</v>
@@ -15688,7 +16215,7 @@
         <v>2.5</v>
       </c>
       <c r="F127" s="5">
-        <f t="shared" si="10"/>
+        <f t="shared" ref="F127" si="9">(B127/E127)*100</f>
         <v>22.000000000000004</v>
       </c>
       <c r="G127" s="5" t="s">
@@ -15717,15 +16244,14 @@
       <c r="E128">
         <v>1.4</v>
       </c>
-      <c r="F128" s="7" t="e">
-        <f t="shared" si="10"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="G128" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="H128" s="7" t="s">
-        <v>23</v>
+      <c r="F128" t="s">
+        <v>10</v>
+      </c>
+      <c r="G128" t="s">
+        <v>10</v>
+      </c>
+      <c r="H128" t="s">
+        <v>10</v>
       </c>
       <c r="I128" t="s">
         <v>73</v>
@@ -15747,15 +16273,14 @@
       <c r="E129">
         <v>700</v>
       </c>
-      <c r="F129" s="7" t="e">
-        <f t="shared" si="10"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="G129" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="H129" s="7" t="s">
-        <v>23</v>
+      <c r="F129" t="s">
+        <v>10</v>
+      </c>
+      <c r="G129" t="s">
+        <v>10</v>
+      </c>
+      <c r="H129" t="s">
+        <v>10</v>
       </c>
       <c r="I129" t="s">
         <v>73</v>
@@ -15777,15 +16302,14 @@
       <c r="E130">
         <v>2000</v>
       </c>
-      <c r="F130" s="7" t="e">
-        <f t="shared" si="10"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="G130" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="H130" s="7" t="s">
-        <v>23</v>
+      <c r="F130" t="s">
+        <v>10</v>
+      </c>
+      <c r="G130" t="s">
+        <v>10</v>
+      </c>
+      <c r="H130" t="s">
+        <v>10</v>
       </c>
       <c r="I130" t="s">
         <v>73</v>
@@ -15807,15 +16331,14 @@
       <c r="E131">
         <v>375</v>
       </c>
-      <c r="F131" s="7" t="e">
-        <f t="shared" si="10"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="G131" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="H131" s="7" t="s">
-        <v>23</v>
+      <c r="F131" t="s">
+        <v>10</v>
+      </c>
+      <c r="G131" t="s">
+        <v>10</v>
+      </c>
+      <c r="H131" t="s">
+        <v>10</v>
       </c>
       <c r="I131" t="s">
         <v>73</v>
@@ -15837,15 +16360,14 @@
       <c r="E132">
         <v>800</v>
       </c>
-      <c r="F132" s="7" t="e">
-        <f t="shared" si="10"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="G132" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="H132" s="7" t="s">
-        <v>23</v>
+      <c r="F132" t="s">
+        <v>10</v>
+      </c>
+      <c r="G132" t="s">
+        <v>10</v>
+      </c>
+      <c r="H132" t="s">
+        <v>10</v>
       </c>
       <c r="I132" t="s">
         <v>73</v>
@@ -15867,15 +16389,14 @@
       <c r="E133">
         <v>5</v>
       </c>
-      <c r="F133" s="7" t="e">
-        <f t="shared" si="10"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="G133" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="H133" s="7" t="s">
-        <v>23</v>
+      <c r="F133" t="s">
+        <v>10</v>
+      </c>
+      <c r="G133" t="s">
+        <v>10</v>
+      </c>
+      <c r="H133" t="s">
+        <v>10</v>
       </c>
       <c r="I133" t="s">
         <v>73</v>
@@ -15902,6 +16423,15 @@
       <c r="E135" s="4" t="s">
         <v>10</v>
       </c>
+      <c r="F135" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G135" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="H135" s="4" t="s">
+        <v>10</v>
+      </c>
       <c r="I135" t="s">
         <v>74</v>
       </c>
@@ -15952,15 +16482,14 @@
       <c r="E137">
         <v>800</v>
       </c>
-      <c r="F137" s="7" t="e">
-        <f>(B137/E137)*100</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="G137" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="H137" s="7" t="s">
-        <v>23</v>
+      <c r="F137" t="s">
+        <v>10</v>
+      </c>
+      <c r="G137" t="s">
+        <v>10</v>
+      </c>
+      <c r="H137" t="s">
+        <v>10</v>
       </c>
       <c r="I137" t="s">
         <v>74</v>
@@ -15982,15 +16511,14 @@
       <c r="E138">
         <v>150</v>
       </c>
-      <c r="F138" s="7" t="e">
-        <f t="shared" ref="F138:F145" si="11">(B138/E138)*100</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="G138" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="H138" s="7" t="s">
-        <v>23</v>
+      <c r="F138" t="s">
+        <v>10</v>
+      </c>
+      <c r="G138" t="s">
+        <v>10</v>
+      </c>
+      <c r="H138" t="s">
+        <v>10</v>
       </c>
       <c r="I138" t="s">
         <v>74</v>
@@ -16012,15 +16540,14 @@
       <c r="E139">
         <v>2.5</v>
       </c>
-      <c r="F139" s="5" t="e">
-        <f t="shared" si="11"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="G139" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="H139" s="7" t="s">
-        <v>23</v>
+      <c r="F139" t="s">
+        <v>10</v>
+      </c>
+      <c r="G139" t="s">
+        <v>10</v>
+      </c>
+      <c r="H139" t="s">
+        <v>10</v>
       </c>
       <c r="I139" t="s">
         <v>74</v>
@@ -16042,15 +16569,14 @@
       <c r="E140">
         <v>1.4</v>
       </c>
-      <c r="F140" s="7" t="e">
-        <f t="shared" si="11"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="G140" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="H140" s="7" t="s">
-        <v>23</v>
+      <c r="F140" t="s">
+        <v>10</v>
+      </c>
+      <c r="G140" t="s">
+        <v>10</v>
+      </c>
+      <c r="H140" t="s">
+        <v>10</v>
       </c>
       <c r="I140" t="s">
         <v>74</v>
@@ -16072,15 +16598,14 @@
       <c r="E141">
         <v>700</v>
       </c>
-      <c r="F141" s="7" t="e">
-        <f t="shared" si="11"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="G141" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="H141" s="7" t="s">
-        <v>23</v>
+      <c r="F141" t="s">
+        <v>10</v>
+      </c>
+      <c r="G141" t="s">
+        <v>10</v>
+      </c>
+      <c r="H141" t="s">
+        <v>10</v>
       </c>
       <c r="I141" t="s">
         <v>74</v>
@@ -16102,15 +16627,14 @@
       <c r="E142">
         <v>2000</v>
       </c>
-      <c r="F142" s="7" t="e">
-        <f t="shared" si="11"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="G142" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="H142" s="7" t="s">
-        <v>23</v>
+      <c r="F142" t="s">
+        <v>10</v>
+      </c>
+      <c r="G142" t="s">
+        <v>10</v>
+      </c>
+      <c r="H142" t="s">
+        <v>10</v>
       </c>
       <c r="I142" t="s">
         <v>74</v>
@@ -16132,15 +16656,14 @@
       <c r="E143">
         <v>375</v>
       </c>
-      <c r="F143" s="7" t="e">
-        <f t="shared" si="11"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="G143" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="H143" s="7" t="s">
-        <v>23</v>
+      <c r="F143" t="s">
+        <v>10</v>
+      </c>
+      <c r="G143" t="s">
+        <v>10</v>
+      </c>
+      <c r="H143" t="s">
+        <v>10</v>
       </c>
       <c r="I143" t="s">
         <v>74</v>
@@ -16162,15 +16685,14 @@
       <c r="E144">
         <v>800</v>
       </c>
-      <c r="F144" s="7" t="e">
-        <f t="shared" si="11"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="G144" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="H144" s="7" t="s">
-        <v>23</v>
+      <c r="F144" t="s">
+        <v>10</v>
+      </c>
+      <c r="G144" t="s">
+        <v>10</v>
+      </c>
+      <c r="H144" t="s">
+        <v>10</v>
       </c>
       <c r="I144" t="s">
         <v>74</v>
@@ -16192,15 +16714,14 @@
       <c r="E145">
         <v>5</v>
       </c>
-      <c r="F145" s="7" t="e">
-        <f t="shared" si="11"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="G145" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="H145" s="7" t="s">
-        <v>23</v>
+      <c r="F145" t="s">
+        <v>10</v>
+      </c>
+      <c r="G145" t="s">
+        <v>10</v>
+      </c>
+      <c r="H145" t="s">
+        <v>10</v>
       </c>
       <c r="I145" t="s">
         <v>74</v>
@@ -16227,6 +16748,15 @@
       <c r="E147" s="4" t="s">
         <v>10</v>
       </c>
+      <c r="F147" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G147" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="H147" s="4" t="s">
+        <v>10</v>
+      </c>
       <c r="I147" t="s">
         <v>74</v>
       </c>
@@ -16277,15 +16807,14 @@
       <c r="E149">
         <v>800</v>
       </c>
-      <c r="F149" s="7" t="e">
-        <f>(B149/E149)*100</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="G149" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="H149" s="7" t="s">
-        <v>23</v>
+      <c r="F149" t="s">
+        <v>10</v>
+      </c>
+      <c r="G149" t="s">
+        <v>10</v>
+      </c>
+      <c r="H149" t="s">
+        <v>10</v>
       </c>
       <c r="I149" t="s">
         <v>74</v>
@@ -16307,15 +16836,14 @@
       <c r="E150">
         <v>150</v>
       </c>
-      <c r="F150" s="7" t="e">
-        <f t="shared" ref="F150:F157" si="12">(B150/E150)*100</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="G150" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="H150" s="7" t="s">
-        <v>23</v>
+      <c r="F150" t="s">
+        <v>10</v>
+      </c>
+      <c r="G150" t="s">
+        <v>10</v>
+      </c>
+      <c r="H150" t="s">
+        <v>10</v>
       </c>
       <c r="I150" t="s">
         <v>74</v>
@@ -16337,15 +16865,14 @@
       <c r="E151">
         <v>2.5</v>
       </c>
-      <c r="F151" s="5" t="e">
-        <f t="shared" si="12"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="G151" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="H151" s="7" t="s">
-        <v>23</v>
+      <c r="F151" t="s">
+        <v>10</v>
+      </c>
+      <c r="G151" t="s">
+        <v>10</v>
+      </c>
+      <c r="H151" t="s">
+        <v>10</v>
       </c>
       <c r="I151" t="s">
         <v>74</v>
@@ -16367,15 +16894,14 @@
       <c r="E152">
         <v>1.4</v>
       </c>
-      <c r="F152" s="7" t="e">
-        <f t="shared" si="12"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="G152" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="H152" s="7" t="s">
-        <v>23</v>
+      <c r="F152" t="s">
+        <v>10</v>
+      </c>
+      <c r="G152" t="s">
+        <v>10</v>
+      </c>
+      <c r="H152" t="s">
+        <v>10</v>
       </c>
       <c r="I152" t="s">
         <v>74</v>
@@ -16397,15 +16923,14 @@
       <c r="E153">
         <v>700</v>
       </c>
-      <c r="F153" s="7" t="e">
-        <f t="shared" si="12"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="G153" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="H153" s="7" t="s">
-        <v>23</v>
+      <c r="F153" t="s">
+        <v>10</v>
+      </c>
+      <c r="G153" t="s">
+        <v>10</v>
+      </c>
+      <c r="H153" t="s">
+        <v>10</v>
       </c>
       <c r="I153" t="s">
         <v>74</v>
@@ -16427,15 +16952,14 @@
       <c r="E154">
         <v>2000</v>
       </c>
-      <c r="F154" s="7" t="e">
-        <f t="shared" si="12"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="G154" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="H154" s="7" t="s">
-        <v>23</v>
+      <c r="F154" t="s">
+        <v>10</v>
+      </c>
+      <c r="G154" t="s">
+        <v>10</v>
+      </c>
+      <c r="H154" t="s">
+        <v>10</v>
       </c>
       <c r="I154" t="s">
         <v>74</v>
@@ -16457,15 +16981,14 @@
       <c r="E155">
         <v>375</v>
       </c>
-      <c r="F155" s="7" t="e">
-        <f t="shared" si="12"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="G155" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="H155" s="7" t="s">
-        <v>23</v>
+      <c r="F155" t="s">
+        <v>10</v>
+      </c>
+      <c r="G155" t="s">
+        <v>10</v>
+      </c>
+      <c r="H155" t="s">
+        <v>10</v>
       </c>
       <c r="I155" t="s">
         <v>74</v>
@@ -16487,15 +17010,14 @@
       <c r="E156">
         <v>800</v>
       </c>
-      <c r="F156" s="7" t="e">
-        <f t="shared" si="12"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="G156" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="H156" s="7" t="s">
-        <v>23</v>
+      <c r="F156" t="s">
+        <v>10</v>
+      </c>
+      <c r="G156" t="s">
+        <v>10</v>
+      </c>
+      <c r="H156" t="s">
+        <v>10</v>
       </c>
       <c r="I156" t="s">
         <v>74</v>
@@ -16517,15 +17039,14 @@
       <c r="E157">
         <v>5</v>
       </c>
-      <c r="F157" s="7" t="e">
-        <f t="shared" si="12"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="G157" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="H157" s="7" t="s">
-        <v>23</v>
+      <c r="F157" t="s">
+        <v>10</v>
+      </c>
+      <c r="G157" t="s">
+        <v>10</v>
+      </c>
+      <c r="H157" t="s">
+        <v>10</v>
       </c>
       <c r="I157" t="s">
         <v>74</v>
@@ -16552,6 +17073,15 @@
       <c r="E159" s="4" t="s">
         <v>10</v>
       </c>
+      <c r="F159" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G159" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="H159" s="4" t="s">
+        <v>10</v>
+      </c>
       <c r="I159" t="s">
         <v>75</v>
       </c>
@@ -16633,7 +17163,7 @@
         <v>150</v>
       </c>
       <c r="F162" s="7">
-        <f t="shared" ref="F162:F169" si="13">(B162/E162)*100</f>
+        <f t="shared" ref="F162:F164" si="10">(B162/E162)*100</f>
         <v>9.3333333333333339</v>
       </c>
       <c r="G162" s="7" t="s">
@@ -16663,7 +17193,7 @@
         <v>2.5</v>
       </c>
       <c r="F163" s="5">
-        <f t="shared" si="13"/>
+        <f t="shared" si="10"/>
         <v>27.999999999999996</v>
       </c>
       <c r="G163" s="5" t="s">
@@ -16693,7 +17223,7 @@
         <v>1.4</v>
       </c>
       <c r="F164" s="7">
-        <f t="shared" si="13"/>
+        <f t="shared" si="10"/>
         <v>10.000000000000002</v>
       </c>
       <c r="G164" s="7" t="s">
@@ -16722,15 +17252,14 @@
       <c r="E165">
         <v>700</v>
       </c>
-      <c r="F165" s="7" t="e">
-        <f t="shared" si="13"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="G165" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="H165" s="7" t="s">
-        <v>23</v>
+      <c r="F165" t="s">
+        <v>10</v>
+      </c>
+      <c r="G165" t="s">
+        <v>10</v>
+      </c>
+      <c r="H165" t="s">
+        <v>10</v>
       </c>
       <c r="I165" t="s">
         <v>75</v>
@@ -16752,15 +17281,14 @@
       <c r="E166">
         <v>2000</v>
       </c>
-      <c r="F166" s="7" t="e">
-        <f t="shared" si="13"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="G166" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="H166" s="7" t="s">
-        <v>23</v>
+      <c r="F166" t="s">
+        <v>10</v>
+      </c>
+      <c r="G166" t="s">
+        <v>10</v>
+      </c>
+      <c r="H166" t="s">
+        <v>10</v>
       </c>
       <c r="I166" t="s">
         <v>75</v>
@@ -16782,15 +17310,14 @@
       <c r="E167">
         <v>375</v>
       </c>
-      <c r="F167" s="7" t="e">
-        <f t="shared" si="13"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="G167" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="H167" s="7" t="s">
-        <v>23</v>
+      <c r="F167" t="s">
+        <v>10</v>
+      </c>
+      <c r="G167" t="s">
+        <v>10</v>
+      </c>
+      <c r="H167" t="s">
+        <v>10</v>
       </c>
       <c r="I167" t="s">
         <v>75</v>
@@ -16812,15 +17339,14 @@
       <c r="E168">
         <v>800</v>
       </c>
-      <c r="F168" s="7" t="e">
-        <f t="shared" si="13"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="G168" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="H168" s="7" t="s">
-        <v>23</v>
+      <c r="F168" t="s">
+        <v>10</v>
+      </c>
+      <c r="G168" t="s">
+        <v>10</v>
+      </c>
+      <c r="H168" t="s">
+        <v>10</v>
       </c>
       <c r="I168" t="s">
         <v>75</v>
@@ -16842,15 +17368,14 @@
       <c r="E169">
         <v>5</v>
       </c>
-      <c r="F169" s="7" t="e">
-        <f t="shared" si="13"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="G169" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="H169" s="7" t="s">
-        <v>23</v>
+      <c r="F169" t="s">
+        <v>10</v>
+      </c>
+      <c r="G169" t="s">
+        <v>10</v>
+      </c>
+      <c r="H169" t="s">
+        <v>10</v>
       </c>
       <c r="I169" t="s">
         <v>75</v>
@@ -16877,6 +17402,15 @@
       <c r="E171" s="4" t="s">
         <v>10</v>
       </c>
+      <c r="F171" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G171" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="H171" s="4" t="s">
+        <v>10</v>
+      </c>
       <c r="I171" t="s">
         <v>76</v>
       </c>
@@ -16927,15 +17461,14 @@
       <c r="E173">
         <v>800</v>
       </c>
-      <c r="F173" s="7" t="e">
-        <f>(B173/E173)*100</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="G173" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="H173" s="7" t="s">
-        <v>23</v>
+      <c r="F173" t="s">
+        <v>10</v>
+      </c>
+      <c r="G173" t="s">
+        <v>10</v>
+      </c>
+      <c r="H173" t="s">
+        <v>10</v>
       </c>
       <c r="I173" t="s">
         <v>76</v>
@@ -16957,15 +17490,14 @@
       <c r="E174">
         <v>150</v>
       </c>
-      <c r="F174" s="7" t="e">
-        <f t="shared" ref="F174:F181" si="14">(B174/E174)*100</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="G174" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="H174" s="7" t="s">
-        <v>23</v>
+      <c r="F174" t="s">
+        <v>10</v>
+      </c>
+      <c r="G174" t="s">
+        <v>10</v>
+      </c>
+      <c r="H174" t="s">
+        <v>10</v>
       </c>
       <c r="I174" t="s">
         <v>76</v>
@@ -16988,7 +17520,7 @@
         <v>2.5</v>
       </c>
       <c r="F175" s="5">
-        <f t="shared" si="14"/>
+        <f t="shared" ref="F175" si="11">(B175/E175)*100</f>
         <v>27.999999999999996</v>
       </c>
       <c r="G175" s="5" t="s">
@@ -17017,15 +17549,14 @@
       <c r="E176">
         <v>1.4</v>
       </c>
-      <c r="F176" s="7" t="e">
-        <f t="shared" si="14"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="G176" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="H176" s="7" t="s">
-        <v>23</v>
+      <c r="F176" t="s">
+        <v>10</v>
+      </c>
+      <c r="G176" t="s">
+        <v>10</v>
+      </c>
+      <c r="H176" t="s">
+        <v>10</v>
       </c>
       <c r="I176" t="s">
         <v>76</v>
@@ -17047,15 +17578,14 @@
       <c r="E177">
         <v>700</v>
       </c>
-      <c r="F177" s="7" t="e">
-        <f t="shared" si="14"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="G177" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="H177" s="7" t="s">
-        <v>23</v>
+      <c r="F177" t="s">
+        <v>10</v>
+      </c>
+      <c r="G177" t="s">
+        <v>10</v>
+      </c>
+      <c r="H177" t="s">
+        <v>10</v>
       </c>
       <c r="I177" t="s">
         <v>76</v>
@@ -17077,15 +17607,14 @@
       <c r="E178">
         <v>2000</v>
       </c>
-      <c r="F178" s="7" t="e">
-        <f t="shared" si="14"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="G178" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="H178" s="7" t="s">
-        <v>23</v>
+      <c r="F178" t="s">
+        <v>10</v>
+      </c>
+      <c r="G178" t="s">
+        <v>10</v>
+      </c>
+      <c r="H178" t="s">
+        <v>10</v>
       </c>
       <c r="I178" t="s">
         <v>76</v>
@@ -17107,15 +17636,14 @@
       <c r="E179">
         <v>375</v>
       </c>
-      <c r="F179" s="7" t="e">
-        <f t="shared" si="14"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="G179" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="H179" s="7" t="s">
-        <v>23</v>
+      <c r="F179" t="s">
+        <v>10</v>
+      </c>
+      <c r="G179" t="s">
+        <v>10</v>
+      </c>
+      <c r="H179" t="s">
+        <v>10</v>
       </c>
       <c r="I179" t="s">
         <v>76</v>
@@ -17137,15 +17665,14 @@
       <c r="E180">
         <v>800</v>
       </c>
-      <c r="F180" s="7" t="e">
-        <f t="shared" si="14"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="G180" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="H180" s="7" t="s">
-        <v>23</v>
+      <c r="F180" t="s">
+        <v>10</v>
+      </c>
+      <c r="G180" t="s">
+        <v>10</v>
+      </c>
+      <c r="H180" t="s">
+        <v>10</v>
       </c>
       <c r="I180" t="s">
         <v>76</v>
@@ -17167,15 +17694,14 @@
       <c r="E181">
         <v>5</v>
       </c>
-      <c r="F181" s="7" t="e">
-        <f t="shared" si="14"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="G181" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="H181" s="7" t="s">
-        <v>23</v>
+      <c r="F181" t="s">
+        <v>10</v>
+      </c>
+      <c r="G181" t="s">
+        <v>10</v>
+      </c>
+      <c r="H181" t="s">
+        <v>10</v>
       </c>
       <c r="I181" t="s">
         <v>76</v>
@@ -17202,6 +17728,15 @@
       <c r="E183" s="4" t="s">
         <v>10</v>
       </c>
+      <c r="F183" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G183" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="H183" s="4" t="s">
+        <v>10</v>
+      </c>
       <c r="I183" t="s">
         <v>77</v>
       </c>
@@ -17282,15 +17817,14 @@
       <c r="E186">
         <v>150</v>
       </c>
-      <c r="F186" s="7" t="e">
-        <f t="shared" ref="F186:F193" si="15">(B186/E186)*100</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="G186" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="H186" s="7" t="s">
-        <v>23</v>
+      <c r="F186" t="s">
+        <v>10</v>
+      </c>
+      <c r="G186" t="s">
+        <v>10</v>
+      </c>
+      <c r="H186" t="s">
+        <v>10</v>
       </c>
       <c r="I186" t="s">
         <v>77</v>
@@ -17313,7 +17847,7 @@
         <v>2.5</v>
       </c>
       <c r="F187" s="5">
-        <f t="shared" si="15"/>
+        <f t="shared" ref="F187" si="12">(B187/E187)*100</f>
         <v>27.999999999999996</v>
       </c>
       <c r="G187" s="5" t="s">
@@ -17342,15 +17876,14 @@
       <c r="E188">
         <v>1.4</v>
       </c>
-      <c r="F188" s="7" t="e">
-        <f t="shared" si="15"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="G188" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="H188" s="7" t="s">
-        <v>23</v>
+      <c r="F188" t="s">
+        <v>10</v>
+      </c>
+      <c r="G188" t="s">
+        <v>10</v>
+      </c>
+      <c r="H188" t="s">
+        <v>10</v>
       </c>
       <c r="I188" t="s">
         <v>77</v>
@@ -17372,15 +17905,14 @@
       <c r="E189">
         <v>700</v>
       </c>
-      <c r="F189" s="7" t="e">
-        <f t="shared" si="15"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="G189" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="H189" s="7" t="s">
-        <v>23</v>
+      <c r="F189" t="s">
+        <v>10</v>
+      </c>
+      <c r="G189" t="s">
+        <v>10</v>
+      </c>
+      <c r="H189" t="s">
+        <v>10</v>
       </c>
       <c r="I189" t="s">
         <v>77</v>
@@ -17402,15 +17934,14 @@
       <c r="E190">
         <v>2000</v>
       </c>
-      <c r="F190" s="7" t="e">
-        <f t="shared" si="15"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="G190" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="H190" s="7" t="s">
-        <v>23</v>
+      <c r="F190" t="s">
+        <v>10</v>
+      </c>
+      <c r="G190" t="s">
+        <v>10</v>
+      </c>
+      <c r="H190" t="s">
+        <v>10</v>
       </c>
       <c r="I190" t="s">
         <v>77</v>
@@ -17432,15 +17963,14 @@
       <c r="E191">
         <v>375</v>
       </c>
-      <c r="F191" s="7" t="e">
-        <f t="shared" si="15"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="G191" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="H191" s="7" t="s">
-        <v>23</v>
+      <c r="F191" t="s">
+        <v>10</v>
+      </c>
+      <c r="G191" t="s">
+        <v>10</v>
+      </c>
+      <c r="H191" t="s">
+        <v>10</v>
       </c>
       <c r="I191" t="s">
         <v>77</v>
@@ -17462,15 +17992,14 @@
       <c r="E192">
         <v>800</v>
       </c>
-      <c r="F192" s="7" t="e">
-        <f t="shared" si="15"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="G192" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="H192" s="7" t="s">
-        <v>23</v>
+      <c r="F192" t="s">
+        <v>10</v>
+      </c>
+      <c r="G192" t="s">
+        <v>10</v>
+      </c>
+      <c r="H192" t="s">
+        <v>10</v>
       </c>
       <c r="I192" t="s">
         <v>77</v>
@@ -17492,15 +18021,14 @@
       <c r="E193">
         <v>5</v>
       </c>
-      <c r="F193" s="7" t="e">
-        <f t="shared" si="15"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="G193" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="H193" s="7" t="s">
-        <v>23</v>
+      <c r="F193" t="s">
+        <v>10</v>
+      </c>
+      <c r="G193" t="s">
+        <v>10</v>
+      </c>
+      <c r="H193" t="s">
+        <v>10</v>
       </c>
       <c r="I193" t="s">
         <v>77</v>
@@ -17527,6 +18055,15 @@
       <c r="E195" s="4" t="s">
         <v>10</v>
       </c>
+      <c r="F195" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G195" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="H195" s="4" t="s">
+        <v>10</v>
+      </c>
       <c r="I195" t="s">
         <v>78</v>
       </c>
@@ -17607,15 +18144,14 @@
       <c r="E198">
         <v>150</v>
       </c>
-      <c r="F198" s="7" t="e">
-        <f t="shared" ref="F198:F205" si="16">(B198/E198)*100</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="G198" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="H198" s="7" t="s">
-        <v>23</v>
+      <c r="F198" t="s">
+        <v>10</v>
+      </c>
+      <c r="G198" t="s">
+        <v>10</v>
+      </c>
+      <c r="H198" t="s">
+        <v>10</v>
       </c>
       <c r="I198" t="s">
         <v>78</v>
@@ -17637,15 +18173,14 @@
       <c r="E199">
         <v>2.5</v>
       </c>
-      <c r="F199" s="5" t="e">
-        <f t="shared" si="16"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="G199" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="H199" s="7" t="s">
-        <v>23</v>
+      <c r="F199" t="s">
+        <v>10</v>
+      </c>
+      <c r="G199" t="s">
+        <v>10</v>
+      </c>
+      <c r="H199" t="s">
+        <v>10</v>
       </c>
       <c r="I199" t="s">
         <v>78</v>
@@ -17667,15 +18202,14 @@
       <c r="E200">
         <v>1.4</v>
       </c>
-      <c r="F200" s="7" t="e">
-        <f t="shared" si="16"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="G200" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="H200" s="7" t="s">
-        <v>23</v>
+      <c r="F200" t="s">
+        <v>10</v>
+      </c>
+      <c r="G200" t="s">
+        <v>10</v>
+      </c>
+      <c r="H200" t="s">
+        <v>10</v>
       </c>
       <c r="I200" t="s">
         <v>78</v>
@@ -17698,7 +18232,7 @@
         <v>700</v>
       </c>
       <c r="F201" s="5">
-        <f t="shared" si="16"/>
+        <f t="shared" ref="F201" si="13">(B201/E201)*100</f>
         <v>21.428571428571427</v>
       </c>
       <c r="G201" s="5" t="s">
@@ -17727,15 +18261,14 @@
       <c r="E202">
         <v>2000</v>
       </c>
-      <c r="F202" s="7" t="e">
-        <f t="shared" si="16"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="G202" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="H202" s="7" t="s">
-        <v>23</v>
+      <c r="F202" t="s">
+        <v>10</v>
+      </c>
+      <c r="G202" t="s">
+        <v>10</v>
+      </c>
+      <c r="H202" t="s">
+        <v>10</v>
       </c>
       <c r="I202" t="s">
         <v>78</v>
@@ -17757,15 +18290,14 @@
       <c r="E203">
         <v>375</v>
       </c>
-      <c r="F203" s="7" t="e">
-        <f t="shared" si="16"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="G203" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="H203" s="7" t="s">
-        <v>23</v>
+      <c r="F203" t="s">
+        <v>10</v>
+      </c>
+      <c r="G203" t="s">
+        <v>10</v>
+      </c>
+      <c r="H203" t="s">
+        <v>10</v>
       </c>
       <c r="I203" t="s">
         <v>78</v>
@@ -17787,15 +18319,14 @@
       <c r="E204">
         <v>800</v>
       </c>
-      <c r="F204" s="7" t="e">
-        <f t="shared" si="16"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="G204" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="H204" s="7" t="s">
-        <v>23</v>
+      <c r="F204" t="s">
+        <v>10</v>
+      </c>
+      <c r="G204" t="s">
+        <v>10</v>
+      </c>
+      <c r="H204" t="s">
+        <v>10</v>
       </c>
       <c r="I204" t="s">
         <v>78</v>
@@ -17817,15 +18348,14 @@
       <c r="E205">
         <v>5</v>
       </c>
-      <c r="F205" s="7" t="e">
-        <f t="shared" si="16"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="G205" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="H205" s="7" t="s">
-        <v>23</v>
+      <c r="F205" t="s">
+        <v>10</v>
+      </c>
+      <c r="G205" t="s">
+        <v>10</v>
+      </c>
+      <c r="H205" t="s">
+        <v>10</v>
       </c>
       <c r="I205" t="s">
         <v>78</v>
@@ -17852,6 +18382,15 @@
       <c r="E207" s="4" t="s">
         <v>10</v>
       </c>
+      <c r="F207" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G207" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="H207" s="4" t="s">
+        <v>10</v>
+      </c>
       <c r="I207" t="s">
         <v>79</v>
       </c>
@@ -17932,15 +18471,14 @@
       <c r="E210">
         <v>150</v>
       </c>
-      <c r="F210" s="7" t="e">
-        <f t="shared" ref="F210:F217" si="17">(B210/E210)*100</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="G210" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="H210" s="7" t="s">
-        <v>23</v>
+      <c r="F210" t="s">
+        <v>10</v>
+      </c>
+      <c r="G210" t="s">
+        <v>10</v>
+      </c>
+      <c r="H210" t="s">
+        <v>10</v>
       </c>
       <c r="I210" t="s">
         <v>79</v>
@@ -17963,7 +18501,7 @@
         <v>2.5</v>
       </c>
       <c r="F211" s="5">
-        <f t="shared" si="17"/>
+        <f t="shared" ref="F211:F213" si="14">(B211/E211)*100</f>
         <v>33.199999999999996</v>
       </c>
       <c r="G211" s="5" t="s">
@@ -17992,15 +18530,14 @@
       <c r="E212">
         <v>1.4</v>
       </c>
-      <c r="F212" s="7" t="e">
-        <f t="shared" si="17"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="G212" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="H212" s="7" t="s">
-        <v>23</v>
+      <c r="F212" t="s">
+        <v>10</v>
+      </c>
+      <c r="G212" t="s">
+        <v>10</v>
+      </c>
+      <c r="H212" t="s">
+        <v>10</v>
       </c>
       <c r="I212" t="s">
         <v>79</v>
@@ -18023,7 +18560,7 @@
         <v>700</v>
       </c>
       <c r="F213" s="5">
-        <f t="shared" si="17"/>
+        <f t="shared" si="14"/>
         <v>20.714285714285715</v>
       </c>
       <c r="G213" s="5" t="s">
@@ -18052,15 +18589,14 @@
       <c r="E214">
         <v>2000</v>
       </c>
-      <c r="F214" s="7" t="e">
-        <f t="shared" si="17"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="G214" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="H214" s="7" t="s">
-        <v>23</v>
+      <c r="F214" t="s">
+        <v>10</v>
+      </c>
+      <c r="G214" t="s">
+        <v>10</v>
+      </c>
+      <c r="H214" t="s">
+        <v>10</v>
       </c>
       <c r="I214" t="s">
         <v>79</v>
@@ -18082,15 +18618,14 @@
       <c r="E215">
         <v>375</v>
       </c>
-      <c r="F215" s="7" t="e">
-        <f t="shared" si="17"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="G215" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="H215" s="7" t="s">
-        <v>23</v>
+      <c r="F215" t="s">
+        <v>10</v>
+      </c>
+      <c r="G215" t="s">
+        <v>10</v>
+      </c>
+      <c r="H215" t="s">
+        <v>10</v>
       </c>
       <c r="I215" t="s">
         <v>79</v>
@@ -18112,15 +18647,14 @@
       <c r="E216">
         <v>800</v>
       </c>
-      <c r="F216" s="7" t="e">
-        <f t="shared" si="17"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="G216" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="H216" s="7" t="s">
-        <v>23</v>
+      <c r="F216" t="s">
+        <v>10</v>
+      </c>
+      <c r="G216" t="s">
+        <v>10</v>
+      </c>
+      <c r="H216" t="s">
+        <v>10</v>
       </c>
       <c r="I216" t="s">
         <v>79</v>
@@ -18142,15 +18676,14 @@
       <c r="E217">
         <v>5</v>
       </c>
-      <c r="F217" s="7" t="e">
-        <f t="shared" si="17"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="G217" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="H217" s="7" t="s">
-        <v>23</v>
+      <c r="F217" t="s">
+        <v>10</v>
+      </c>
+      <c r="G217" t="s">
+        <v>10</v>
+      </c>
+      <c r="H217" t="s">
+        <v>10</v>
       </c>
       <c r="I217" t="s">
         <v>79</v>
@@ -18177,6 +18710,15 @@
       <c r="E219" s="4" t="s">
         <v>10</v>
       </c>
+      <c r="F219" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G219" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="H219" s="4" t="s">
+        <v>10</v>
+      </c>
       <c r="I219" t="s">
         <v>80</v>
       </c>
@@ -18257,15 +18799,14 @@
       <c r="E222">
         <v>150</v>
       </c>
-      <c r="F222" s="7" t="e">
-        <f t="shared" ref="F222:F229" si="18">(B222/E222)*100</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="G222" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="H222" s="7" t="s">
-        <v>23</v>
+      <c r="F222" t="s">
+        <v>10</v>
+      </c>
+      <c r="G222" t="s">
+        <v>10</v>
+      </c>
+      <c r="H222" t="s">
+        <v>10</v>
       </c>
       <c r="I222" t="s">
         <v>80</v>
@@ -18288,7 +18829,7 @@
         <v>2.5</v>
       </c>
       <c r="F223" s="5">
-        <f t="shared" si="18"/>
+        <f t="shared" ref="F223:F225" si="15">(B223/E223)*100</f>
         <v>33.199999999999996</v>
       </c>
       <c r="G223" s="5" t="s">
@@ -18317,15 +18858,14 @@
       <c r="E224">
         <v>1.4</v>
       </c>
-      <c r="F224" s="7" t="e">
-        <f t="shared" si="18"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="G224" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="H224" s="7" t="s">
-        <v>23</v>
+      <c r="F224" t="s">
+        <v>10</v>
+      </c>
+      <c r="G224" t="s">
+        <v>10</v>
+      </c>
+      <c r="H224" t="s">
+        <v>10</v>
       </c>
       <c r="I224" t="s">
         <v>80</v>
@@ -18348,7 +18888,7 @@
         <v>700</v>
       </c>
       <c r="F225" s="5">
-        <f t="shared" si="18"/>
+        <f t="shared" si="15"/>
         <v>20.714285714285715</v>
       </c>
       <c r="G225" s="5" t="s">
@@ -18377,15 +18917,14 @@
       <c r="E226">
         <v>2000</v>
       </c>
-      <c r="F226" s="7" t="e">
-        <f t="shared" si="18"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="G226" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="H226" s="7" t="s">
-        <v>23</v>
+      <c r="F226" t="s">
+        <v>10</v>
+      </c>
+      <c r="G226" t="s">
+        <v>10</v>
+      </c>
+      <c r="H226" t="s">
+        <v>10</v>
       </c>
       <c r="I226" t="s">
         <v>80</v>
@@ -18407,15 +18946,14 @@
       <c r="E227">
         <v>375</v>
       </c>
-      <c r="F227" s="7" t="e">
-        <f t="shared" si="18"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="G227" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="H227" s="7" t="s">
-        <v>23</v>
+      <c r="F227" t="s">
+        <v>10</v>
+      </c>
+      <c r="G227" t="s">
+        <v>10</v>
+      </c>
+      <c r="H227" t="s">
+        <v>10</v>
       </c>
       <c r="I227" t="s">
         <v>80</v>
@@ -18437,15 +18975,14 @@
       <c r="E228">
         <v>800</v>
       </c>
-      <c r="F228" s="7" t="e">
-        <f t="shared" si="18"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="G228" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="H228" s="7" t="s">
-        <v>23</v>
+      <c r="F228" t="s">
+        <v>10</v>
+      </c>
+      <c r="G228" t="s">
+        <v>10</v>
+      </c>
+      <c r="H228" t="s">
+        <v>10</v>
       </c>
       <c r="I228" t="s">
         <v>80</v>
@@ -18467,15 +19004,14 @@
       <c r="E229">
         <v>5</v>
       </c>
-      <c r="F229" s="7" t="e">
-        <f t="shared" si="18"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="G229" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="H229" s="7" t="s">
-        <v>23</v>
+      <c r="F229" t="s">
+        <v>10</v>
+      </c>
+      <c r="G229" t="s">
+        <v>10</v>
+      </c>
+      <c r="H229" t="s">
+        <v>10</v>
       </c>
       <c r="I229" t="s">
         <v>80</v>
@@ -18502,6 +19038,15 @@
       <c r="E231" s="4" t="s">
         <v>10</v>
       </c>
+      <c r="F231" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G231" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="H231" s="4" t="s">
+        <v>10</v>
+      </c>
       <c r="I231" t="s">
         <v>81</v>
       </c>
@@ -18582,15 +19127,14 @@
       <c r="E234">
         <v>150</v>
       </c>
-      <c r="F234" s="7" t="e">
-        <f t="shared" ref="F234:F241" si="19">(B234/E234)*100</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="G234" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="H234" s="7" t="s">
-        <v>23</v>
+      <c r="F234" t="s">
+        <v>10</v>
+      </c>
+      <c r="G234" t="s">
+        <v>10</v>
+      </c>
+      <c r="H234" t="s">
+        <v>10</v>
       </c>
       <c r="I234" t="s">
         <v>81</v>
@@ -18613,7 +19157,7 @@
         <v>2.5</v>
       </c>
       <c r="F235" s="5">
-        <f t="shared" si="19"/>
+        <f t="shared" ref="F235:F237" si="16">(B235/E235)*100</f>
         <v>31.6</v>
       </c>
       <c r="G235" s="5" t="s">
@@ -18642,15 +19186,14 @@
       <c r="E236">
         <v>1.4</v>
       </c>
-      <c r="F236" s="7" t="e">
-        <f t="shared" si="19"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="G236" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="H236" s="7" t="s">
-        <v>23</v>
+      <c r="F236" t="s">
+        <v>10</v>
+      </c>
+      <c r="G236" t="s">
+        <v>10</v>
+      </c>
+      <c r="H236" t="s">
+        <v>10</v>
       </c>
       <c r="I236" t="s">
         <v>81</v>
@@ -18673,7 +19216,7 @@
         <v>700</v>
       </c>
       <c r="F237" s="5">
-        <f t="shared" si="19"/>
+        <f t="shared" si="16"/>
         <v>19.714285714285715</v>
       </c>
       <c r="G237" s="5" t="s">
@@ -18702,15 +19245,14 @@
       <c r="E238">
         <v>2000</v>
       </c>
-      <c r="F238" s="7" t="e">
-        <f t="shared" si="19"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="G238" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="H238" s="7" t="s">
-        <v>23</v>
+      <c r="F238" t="s">
+        <v>10</v>
+      </c>
+      <c r="G238" t="s">
+        <v>10</v>
+      </c>
+      <c r="H238" t="s">
+        <v>10</v>
       </c>
       <c r="I238" t="s">
         <v>81</v>
@@ -18732,15 +19274,14 @@
       <c r="E239">
         <v>375</v>
       </c>
-      <c r="F239" s="7" t="e">
-        <f t="shared" si="19"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="G239" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="H239" s="7" t="s">
-        <v>23</v>
+      <c r="F239" t="s">
+        <v>10</v>
+      </c>
+      <c r="G239" t="s">
+        <v>10</v>
+      </c>
+      <c r="H239" t="s">
+        <v>10</v>
       </c>
       <c r="I239" t="s">
         <v>81</v>
@@ -18762,15 +19303,14 @@
       <c r="E240">
         <v>800</v>
       </c>
-      <c r="F240" s="7" t="e">
-        <f t="shared" si="19"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="G240" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="H240" s="7" t="s">
-        <v>23</v>
+      <c r="F240" t="s">
+        <v>10</v>
+      </c>
+      <c r="G240" t="s">
+        <v>10</v>
+      </c>
+      <c r="H240" t="s">
+        <v>10</v>
       </c>
       <c r="I240" t="s">
         <v>81</v>
@@ -18792,15 +19332,14 @@
       <c r="E241">
         <v>5</v>
       </c>
-      <c r="F241" s="7" t="e">
-        <f t="shared" si="19"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="G241" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="H241" s="7" t="s">
-        <v>23</v>
+      <c r="F241" t="s">
+        <v>10</v>
+      </c>
+      <c r="G241" t="s">
+        <v>10</v>
+      </c>
+      <c r="H241" t="s">
+        <v>10</v>
       </c>
       <c r="I241" t="s">
         <v>81</v>
@@ -18866,6 +19405,15 @@
       <c r="E3" s="4" t="s">
         <v>10</v>
       </c>
+      <c r="F3" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G3" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="H3" s="4" t="s">
+        <v>10</v>
+      </c>
       <c r="I3" t="s">
         <v>85</v>
       </c>
@@ -18947,7 +19495,7 @@
         <v>150</v>
       </c>
       <c r="F6" s="5">
-        <f t="shared" ref="F6:F13" si="0">(B6/E6)*100</f>
+        <f t="shared" ref="F6:F12" si="0">(B6/E6)*100</f>
         <v>20</v>
       </c>
       <c r="G6" s="5" t="s">
@@ -19156,15 +19704,14 @@
       <c r="E13">
         <v>5</v>
       </c>
-      <c r="F13" s="7" t="e">
-        <f t="shared" si="0"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="G13" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="H13" s="7" t="s">
-        <v>23</v>
+      <c r="F13" t="s">
+        <v>10</v>
+      </c>
+      <c r="G13" t="s">
+        <v>10</v>
+      </c>
+      <c r="H13" t="s">
+        <v>10</v>
       </c>
       <c r="I13" t="s">
         <v>85</v>
@@ -19191,6 +19738,15 @@
       <c r="E15" s="4" t="s">
         <v>10</v>
       </c>
+      <c r="F15" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G15" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="H15" s="4" t="s">
+        <v>10</v>
+      </c>
       <c r="I15" t="s">
         <v>84</v>
       </c>
@@ -19516,6 +20072,15 @@
       <c r="E27" s="4" t="s">
         <v>10</v>
       </c>
+      <c r="F27" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G27" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="H27" s="4" t="s">
+        <v>10</v>
+      </c>
       <c r="I27" t="s">
         <v>83</v>
       </c>
@@ -19841,6 +20406,15 @@
       <c r="E39" s="4" t="s">
         <v>10</v>
       </c>
+      <c r="F39" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G39" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="H39" s="4" t="s">
+        <v>10</v>
+      </c>
       <c r="I39" t="s">
         <v>82</v>
       </c>
@@ -20163,7 +20737,16 @@
       <c r="D51" t="s">
         <v>10</v>
       </c>
-      <c r="E51" s="4" t="s">
+      <c r="E51" t="s">
+        <v>10</v>
+      </c>
+      <c r="F51" t="s">
+        <v>10</v>
+      </c>
+      <c r="G51" t="s">
+        <v>10</v>
+      </c>
+      <c r="H51" t="s">
         <v>10</v>
       </c>
       <c r="I51" t="s">
@@ -20491,6 +21074,15 @@
       <c r="E63" s="4" t="s">
         <v>10</v>
       </c>
+      <c r="F63" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G63" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="H63" s="4" t="s">
+        <v>10</v>
+      </c>
       <c r="I63" t="s">
         <v>87</v>
       </c>
@@ -20816,6 +21408,15 @@
       <c r="E75" s="4" t="s">
         <v>10</v>
       </c>
+      <c r="F75" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G75" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="H75" s="4" t="s">
+        <v>10</v>
+      </c>
       <c r="I75" t="s">
         <v>88</v>
       </c>
@@ -20866,15 +21467,14 @@
       <c r="E77">
         <v>800</v>
       </c>
-      <c r="F77" s="7" t="e">
-        <f>(B77/E77)*100</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="G77" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="H77" s="7" t="s">
-        <v>23</v>
+      <c r="F77" t="s">
+        <v>10</v>
+      </c>
+      <c r="G77" t="s">
+        <v>10</v>
+      </c>
+      <c r="H77" t="s">
+        <v>10</v>
       </c>
       <c r="I77" t="s">
         <v>88</v>
@@ -20896,15 +21496,14 @@
       <c r="E78">
         <v>150</v>
       </c>
-      <c r="F78" s="7" t="e">
-        <f t="shared" ref="F78:F85" si="6">(B78/E78)*100</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="G78" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="H78" s="7" t="s">
-        <v>23</v>
+      <c r="F78" t="s">
+        <v>10</v>
+      </c>
+      <c r="G78" t="s">
+        <v>10</v>
+      </c>
+      <c r="H78" t="s">
+        <v>10</v>
       </c>
       <c r="I78" t="s">
         <v>88</v>
@@ -20926,15 +21525,14 @@
       <c r="E79">
         <v>2.5</v>
       </c>
-      <c r="F79" s="5" t="e">
-        <f t="shared" si="6"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="G79" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="H79" s="7" t="s">
-        <v>23</v>
+      <c r="F79" t="s">
+        <v>10</v>
+      </c>
+      <c r="G79" t="s">
+        <v>10</v>
+      </c>
+      <c r="H79" t="s">
+        <v>10</v>
       </c>
       <c r="I79" t="s">
         <v>88</v>
@@ -20956,15 +21554,14 @@
       <c r="E80">
         <v>1.4</v>
       </c>
-      <c r="F80" s="7" t="e">
-        <f t="shared" si="6"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="G80" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="H80" s="7" t="s">
-        <v>23</v>
+      <c r="F80" t="s">
+        <v>10</v>
+      </c>
+      <c r="G80" t="s">
+        <v>10</v>
+      </c>
+      <c r="H80" t="s">
+        <v>10</v>
       </c>
       <c r="I80" t="s">
         <v>88</v>
@@ -20987,7 +21584,7 @@
         <v>700</v>
       </c>
       <c r="F81" s="5">
-        <f t="shared" si="6"/>
+        <f t="shared" ref="F81" si="6">(B81/E81)*100</f>
         <v>23.571428571428569</v>
       </c>
       <c r="G81" s="5" t="s">
@@ -21016,15 +21613,14 @@
       <c r="E82">
         <v>2000</v>
       </c>
-      <c r="F82" s="7" t="e">
-        <f t="shared" si="6"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="G82" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="H82" s="7" t="s">
-        <v>23</v>
+      <c r="F82" t="s">
+        <v>10</v>
+      </c>
+      <c r="G82" t="s">
+        <v>10</v>
+      </c>
+      <c r="H82" t="s">
+        <v>10</v>
       </c>
       <c r="I82" t="s">
         <v>88</v>
@@ -21046,15 +21642,14 @@
       <c r="E83">
         <v>375</v>
       </c>
-      <c r="F83" s="7" t="e">
-        <f t="shared" si="6"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="G83" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="H83" s="7" t="s">
-        <v>23</v>
+      <c r="F83" t="s">
+        <v>10</v>
+      </c>
+      <c r="G83" t="s">
+        <v>10</v>
+      </c>
+      <c r="H83" t="s">
+        <v>10</v>
       </c>
       <c r="I83" t="s">
         <v>88</v>
@@ -21076,15 +21671,14 @@
       <c r="E84">
         <v>800</v>
       </c>
-      <c r="F84" s="7" t="e">
-        <f t="shared" si="6"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="G84" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="H84" s="7" t="s">
-        <v>23</v>
+      <c r="F84" t="s">
+        <v>10</v>
+      </c>
+      <c r="G84" t="s">
+        <v>10</v>
+      </c>
+      <c r="H84" t="s">
+        <v>10</v>
       </c>
       <c r="I84" t="s">
         <v>88</v>
@@ -21106,15 +21700,14 @@
       <c r="E85">
         <v>5</v>
       </c>
-      <c r="F85" s="7" t="e">
-        <f t="shared" si="6"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="G85" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="H85" s="7" t="s">
-        <v>23</v>
+      <c r="F85" t="s">
+        <v>10</v>
+      </c>
+      <c r="G85" t="s">
+        <v>10</v>
+      </c>
+      <c r="H85" t="s">
+        <v>10</v>
       </c>
       <c r="I85" t="s">
         <v>88</v>
@@ -21141,6 +21734,15 @@
       <c r="E87" s="4" t="s">
         <v>10</v>
       </c>
+      <c r="F87" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G87" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="H87" s="4" t="s">
+        <v>10</v>
+      </c>
       <c r="I87" t="s">
         <v>89</v>
       </c>
@@ -21191,15 +21793,14 @@
       <c r="E89">
         <v>800</v>
       </c>
-      <c r="F89" s="7" t="e">
-        <f>(B89/E89)*100</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="G89" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="H89" s="7" t="s">
-        <v>23</v>
+      <c r="F89" t="s">
+        <v>10</v>
+      </c>
+      <c r="G89" t="s">
+        <v>10</v>
+      </c>
+      <c r="H89" t="s">
+        <v>10</v>
       </c>
       <c r="I89" t="s">
         <v>89</v>
@@ -21221,15 +21822,14 @@
       <c r="E90">
         <v>150</v>
       </c>
-      <c r="F90" s="7" t="e">
-        <f t="shared" ref="F90:F97" si="7">(B90/E90)*100</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="G90" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="H90" s="7" t="s">
-        <v>23</v>
+      <c r="F90" t="s">
+        <v>10</v>
+      </c>
+      <c r="G90" t="s">
+        <v>10</v>
+      </c>
+      <c r="H90" t="s">
+        <v>10</v>
       </c>
       <c r="I90" t="s">
         <v>89</v>
@@ -21251,15 +21851,14 @@
       <c r="E91">
         <v>2.5</v>
       </c>
-      <c r="F91" s="5" t="e">
-        <f t="shared" si="7"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="G91" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="H91" s="7" t="s">
-        <v>23</v>
+      <c r="F91" t="s">
+        <v>10</v>
+      </c>
+      <c r="G91" t="s">
+        <v>10</v>
+      </c>
+      <c r="H91" t="s">
+        <v>10</v>
       </c>
       <c r="I91" t="s">
         <v>89</v>
@@ -21281,15 +21880,14 @@
       <c r="E92">
         <v>1.4</v>
       </c>
-      <c r="F92" s="7" t="e">
-        <f t="shared" si="7"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="G92" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="H92" s="7" t="s">
-        <v>23</v>
+      <c r="F92" t="s">
+        <v>10</v>
+      </c>
+      <c r="G92" t="s">
+        <v>10</v>
+      </c>
+      <c r="H92" t="s">
+        <v>10</v>
       </c>
       <c r="I92" t="s">
         <v>89</v>
@@ -21312,7 +21910,7 @@
         <v>700</v>
       </c>
       <c r="F93" s="5">
-        <f t="shared" si="7"/>
+        <f t="shared" ref="F93" si="7">(B93/E93)*100</f>
         <v>21.571428571428573</v>
       </c>
       <c r="G93" s="5" t="s">
@@ -21341,15 +21939,14 @@
       <c r="E94">
         <v>2000</v>
       </c>
-      <c r="F94" s="7" t="e">
-        <f t="shared" si="7"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="G94" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="H94" s="7" t="s">
-        <v>23</v>
+      <c r="F94" t="s">
+        <v>10</v>
+      </c>
+      <c r="G94" t="s">
+        <v>10</v>
+      </c>
+      <c r="H94" t="s">
+        <v>10</v>
       </c>
       <c r="I94" t="s">
         <v>89</v>
@@ -21371,15 +21968,14 @@
       <c r="E95">
         <v>375</v>
       </c>
-      <c r="F95" s="7" t="e">
-        <f t="shared" si="7"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="G95" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="H95" s="7" t="s">
-        <v>23</v>
+      <c r="F95" t="s">
+        <v>10</v>
+      </c>
+      <c r="G95" t="s">
+        <v>10</v>
+      </c>
+      <c r="H95" t="s">
+        <v>10</v>
       </c>
       <c r="I95" t="s">
         <v>89</v>
@@ -21401,15 +21997,14 @@
       <c r="E96">
         <v>800</v>
       </c>
-      <c r="F96" s="7" t="e">
-        <f t="shared" si="7"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="G96" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="H96" s="7" t="s">
-        <v>23</v>
+      <c r="F96" t="s">
+        <v>10</v>
+      </c>
+      <c r="G96" t="s">
+        <v>10</v>
+      </c>
+      <c r="H96" t="s">
+        <v>10</v>
       </c>
       <c r="I96" t="s">
         <v>89</v>
@@ -21431,15 +22026,14 @@
       <c r="E97">
         <v>5</v>
       </c>
-      <c r="F97" s="7" t="e">
-        <f t="shared" si="7"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="G97" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="H97" s="7" t="s">
-        <v>23</v>
+      <c r="F97" t="s">
+        <v>10</v>
+      </c>
+      <c r="G97" t="s">
+        <v>10</v>
+      </c>
+      <c r="H97" t="s">
+        <v>10</v>
       </c>
       <c r="I97" t="s">
         <v>89</v>
@@ -21505,6 +22099,15 @@
       <c r="E3" s="4" t="s">
         <v>10</v>
       </c>
+      <c r="F3" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G3" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="H3" s="4" t="s">
+        <v>10</v>
+      </c>
       <c r="I3" t="s">
         <v>90</v>
       </c>
@@ -21585,15 +22188,14 @@
       <c r="E6">
         <v>150</v>
       </c>
-      <c r="F6" s="5" t="e">
-        <f t="shared" ref="F6:F13" si="0">(B6/E6)*100</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="G6" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="H6" s="7" t="s">
-        <v>23</v>
+      <c r="F6" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G6" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="H6" s="4" t="s">
+        <v>10</v>
       </c>
       <c r="I6" t="s">
         <v>90</v>
@@ -21615,15 +22217,14 @@
       <c r="E7">
         <v>2.5</v>
       </c>
-      <c r="F7" s="5" t="e">
-        <f t="shared" si="0"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="G7" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="H7" s="5" t="s">
-        <v>49</v>
+      <c r="F7" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G7" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="H7" s="4" t="s">
+        <v>10</v>
       </c>
       <c r="I7" t="s">
         <v>90</v>
@@ -21645,15 +22246,14 @@
       <c r="E8">
         <v>1.4</v>
       </c>
-      <c r="F8" s="5" t="e">
-        <f t="shared" si="0"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="G8" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="H8" s="7" t="s">
-        <v>23</v>
+      <c r="F8" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G8" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="H8" s="4" t="s">
+        <v>10</v>
       </c>
       <c r="I8" t="s">
         <v>90</v>
@@ -21675,15 +22275,14 @@
       <c r="E9">
         <v>700</v>
       </c>
-      <c r="F9" s="5" t="e">
-        <f t="shared" si="0"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="G9" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="H9" s="5" t="s">
-        <v>49</v>
+      <c r="F9" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G9" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="H9" s="4" t="s">
+        <v>10</v>
       </c>
       <c r="I9" t="s">
         <v>90</v>
@@ -21705,15 +22304,14 @@
       <c r="E10">
         <v>2000</v>
       </c>
-      <c r="F10" s="7" t="e">
-        <f t="shared" si="0"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="G10" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="H10" s="7" t="s">
-        <v>23</v>
+      <c r="F10" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G10" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="H10" s="4" t="s">
+        <v>10</v>
       </c>
       <c r="I10" t="s">
         <v>90</v>
@@ -21735,15 +22333,14 @@
       <c r="E11">
         <v>375</v>
       </c>
-      <c r="F11" s="7" t="e">
-        <f t="shared" si="0"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="G11" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="H11" s="7" t="s">
-        <v>23</v>
+      <c r="F11" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G11" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="H11" s="4" t="s">
+        <v>10</v>
       </c>
       <c r="I11" t="s">
         <v>90</v>
@@ -21765,15 +22362,14 @@
       <c r="E12">
         <v>800</v>
       </c>
-      <c r="F12" s="5" t="e">
-        <f t="shared" si="0"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="G12" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="H12" s="7" t="s">
-        <v>23</v>
+      <c r="F12" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G12" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="H12" s="4" t="s">
+        <v>10</v>
       </c>
       <c r="I12" t="s">
         <v>90</v>
@@ -21795,15 +22391,14 @@
       <c r="E13">
         <v>5</v>
       </c>
-      <c r="F13" s="7" t="e">
-        <f t="shared" si="0"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="G13" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="H13" s="7" t="s">
-        <v>23</v>
+      <c r="F13" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G13" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="H13" s="4" t="s">
+        <v>10</v>
       </c>
       <c r="I13" t="s">
         <v>90</v>
@@ -21830,6 +22425,15 @@
       <c r="E15" s="4" t="s">
         <v>10</v>
       </c>
+      <c r="F15" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G15" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="H15" s="4" t="s">
+        <v>10</v>
+      </c>
       <c r="I15" t="s">
         <v>91</v>
       </c>
@@ -21910,15 +22514,14 @@
       <c r="E18">
         <v>150</v>
       </c>
-      <c r="F18" s="5" t="e">
-        <f t="shared" ref="F18:F25" si="1">(B18/E18)*100</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="G18" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="H18" s="7" t="s">
-        <v>23</v>
+      <c r="F18" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G18" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="H18" s="4" t="s">
+        <v>10</v>
       </c>
       <c r="I18" t="s">
         <v>91</v>
@@ -21940,15 +22543,14 @@
       <c r="E19">
         <v>2.5</v>
       </c>
-      <c r="F19" s="5" t="e">
-        <f t="shared" si="1"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="G19" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="H19" s="5" t="s">
-        <v>49</v>
+      <c r="F19" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G19" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="H19" s="4" t="s">
+        <v>10</v>
       </c>
       <c r="I19" t="s">
         <v>91</v>
@@ -21970,15 +22572,14 @@
       <c r="E20">
         <v>1.4</v>
       </c>
-      <c r="F20" s="5" t="e">
-        <f t="shared" si="1"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="G20" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="H20" s="7" t="s">
-        <v>23</v>
+      <c r="F20" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G20" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="H20" s="4" t="s">
+        <v>10</v>
       </c>
       <c r="I20" t="s">
         <v>91</v>
@@ -22000,15 +22601,14 @@
       <c r="E21">
         <v>700</v>
       </c>
-      <c r="F21" s="5" t="e">
-        <f t="shared" si="1"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="G21" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="H21" s="5" t="s">
-        <v>49</v>
+      <c r="F21" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G21" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="H21" s="4" t="s">
+        <v>10</v>
       </c>
       <c r="I21" t="s">
         <v>91</v>
@@ -22030,15 +22630,14 @@
       <c r="E22">
         <v>2000</v>
       </c>
-      <c r="F22" s="7" t="e">
-        <f t="shared" si="1"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="G22" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="H22" s="7" t="s">
-        <v>23</v>
+      <c r="F22" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G22" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="H22" s="4" t="s">
+        <v>10</v>
       </c>
       <c r="I22" t="s">
         <v>91</v>
@@ -22060,15 +22659,14 @@
       <c r="E23">
         <v>375</v>
       </c>
-      <c r="F23" s="7" t="e">
-        <f t="shared" si="1"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="G23" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="H23" s="7" t="s">
-        <v>23</v>
+      <c r="F23" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G23" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="H23" s="4" t="s">
+        <v>10</v>
       </c>
       <c r="I23" t="s">
         <v>91</v>
@@ -22090,15 +22688,14 @@
       <c r="E24">
         <v>800</v>
       </c>
-      <c r="F24" s="5" t="e">
-        <f t="shared" si="1"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="G24" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="H24" s="7" t="s">
-        <v>23</v>
+      <c r="F24" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G24" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="H24" s="4" t="s">
+        <v>10</v>
       </c>
       <c r="I24" t="s">
         <v>91</v>
@@ -22120,15 +22717,14 @@
       <c r="E25">
         <v>5</v>
       </c>
-      <c r="F25" s="7" t="e">
-        <f t="shared" si="1"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="G25" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="H25" s="7" t="s">
-        <v>23</v>
+      <c r="F25" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G25" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="H25" s="4" t="s">
+        <v>10</v>
       </c>
       <c r="I25" t="s">
         <v>91</v>
@@ -22155,6 +22751,15 @@
       <c r="E27" s="4" t="s">
         <v>10</v>
       </c>
+      <c r="F27" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G27" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="H27" s="4" t="s">
+        <v>10</v>
+      </c>
       <c r="I27" t="s">
         <v>92</v>
       </c>
@@ -22205,9 +22810,8 @@
       <c r="E29">
         <v>800</v>
       </c>
-      <c r="F29" s="5" t="e">
-        <f>(B29/E29)*100</f>
-        <v>#VALUE!</v>
+      <c r="F29" s="4" t="s">
+        <v>10</v>
       </c>
       <c r="G29" s="5" t="s">
         <v>20</v>
@@ -22236,7 +22840,7 @@
         <v>150</v>
       </c>
       <c r="F30" s="5">
-        <f t="shared" ref="F30:F37" si="2">(B30/E30)*100</f>
+        <f t="shared" ref="F30:F36" si="0">(B30/E30)*100</f>
         <v>26</v>
       </c>
       <c r="G30" s="5" t="s">
@@ -22265,9 +22869,8 @@
       <c r="E31">
         <v>2.5</v>
       </c>
-      <c r="F31" s="5" t="e">
-        <f t="shared" si="2"/>
-        <v>#VALUE!</v>
+      <c r="F31" s="4" t="s">
+        <v>10</v>
       </c>
       <c r="G31" s="5" t="s">
         <v>20</v>
@@ -22295,15 +22898,14 @@
       <c r="E32">
         <v>1.4</v>
       </c>
-      <c r="F32" s="5" t="e">
-        <f t="shared" si="2"/>
-        <v>#VALUE!</v>
+      <c r="F32" s="4" t="s">
+        <v>10</v>
       </c>
       <c r="G32" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="H32" s="7" t="s">
-        <v>23</v>
+      <c r="H32" s="4" t="s">
+        <v>10</v>
       </c>
       <c r="I32" t="s">
         <v>92</v>
@@ -22326,14 +22928,14 @@
         <v>700</v>
       </c>
       <c r="F33" s="5">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>15</v>
       </c>
       <c r="G33" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="H33" s="7" t="s">
-        <v>23</v>
+      <c r="H33" s="4" t="s">
+        <v>10</v>
       </c>
       <c r="I33" t="s">
         <v>92</v>
@@ -22355,15 +22957,14 @@
       <c r="E34">
         <v>2000</v>
       </c>
-      <c r="F34" s="7" t="e">
-        <f t="shared" si="2"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="G34" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="H34" s="7" t="s">
-        <v>23</v>
+      <c r="F34" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G34" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="H34" s="4" t="s">
+        <v>10</v>
       </c>
       <c r="I34" t="s">
         <v>92</v>
@@ -22385,15 +22986,14 @@
       <c r="E35">
         <v>375</v>
       </c>
-      <c r="F35" s="7" t="e">
-        <f t="shared" si="2"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="G35" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="H35" s="7" t="s">
-        <v>23</v>
+      <c r="F35" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G35" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="H35" s="4" t="s">
+        <v>10</v>
       </c>
       <c r="I35" t="s">
         <v>92</v>
@@ -22416,7 +23016,7 @@
         <v>800</v>
       </c>
       <c r="F36" s="5">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>31.374999999999996</v>
       </c>
       <c r="G36" s="5" t="s">
@@ -22445,15 +23045,14 @@
       <c r="E37">
         <v>5</v>
       </c>
-      <c r="F37" s="7" t="e">
-        <f t="shared" si="2"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="G37" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="H37" s="7" t="s">
-        <v>23</v>
+      <c r="F37" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G37" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="H37" s="4" t="s">
+        <v>10</v>
       </c>
       <c r="I37" t="s">
         <v>92</v>
@@ -22480,6 +23079,15 @@
       <c r="E39" s="4" t="s">
         <v>10</v>
       </c>
+      <c r="F39" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G39" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="H39" s="4" t="s">
+        <v>10</v>
+      </c>
       <c r="I39" t="s">
         <v>93</v>
       </c>
@@ -22530,9 +23138,8 @@
       <c r="E41">
         <v>800</v>
       </c>
-      <c r="F41" s="5" t="e">
-        <f>(B41/E41)*100</f>
-        <v>#VALUE!</v>
+      <c r="F41" s="4" t="s">
+        <v>10</v>
       </c>
       <c r="G41" s="5" t="s">
         <v>20</v>
@@ -22561,7 +23168,7 @@
         <v>150</v>
       </c>
       <c r="F42" s="5">
-        <f t="shared" ref="F42:F49" si="3">(B42/E42)*100</f>
+        <f t="shared" ref="F42:F48" si="1">(B42/E42)*100</f>
         <v>23.266666666666666</v>
       </c>
       <c r="G42" s="5" t="s">
@@ -22590,9 +23197,8 @@
       <c r="E43">
         <v>2.5</v>
       </c>
-      <c r="F43" s="5" t="e">
-        <f t="shared" si="3"/>
-        <v>#VALUE!</v>
+      <c r="F43" s="4" t="s">
+        <v>10</v>
       </c>
       <c r="G43" s="5" t="s">
         <v>20</v>
@@ -22620,9 +23226,8 @@
       <c r="E44">
         <v>1.4</v>
       </c>
-      <c r="F44" s="5" t="e">
-        <f t="shared" si="3"/>
-        <v>#VALUE!</v>
+      <c r="F44" s="4" t="s">
+        <v>10</v>
       </c>
       <c r="G44" s="5" t="s">
         <v>20</v>
@@ -22650,9 +23255,8 @@
       <c r="E45">
         <v>700</v>
       </c>
-      <c r="F45" s="5" t="e">
-        <f t="shared" si="3"/>
-        <v>#VALUE!</v>
+      <c r="F45" s="4" t="s">
+        <v>10</v>
       </c>
       <c r="G45" s="5" t="s">
         <v>20</v>
@@ -22680,9 +23284,8 @@
       <c r="E46">
         <v>2000</v>
       </c>
-      <c r="F46" s="7" t="e">
-        <f t="shared" si="3"/>
-        <v>#VALUE!</v>
+      <c r="F46" s="4" t="s">
+        <v>10</v>
       </c>
       <c r="G46" s="7" t="s">
         <v>23</v>
@@ -22710,9 +23313,8 @@
       <c r="E47">
         <v>375</v>
       </c>
-      <c r="F47" s="7" t="e">
-        <f t="shared" si="3"/>
-        <v>#VALUE!</v>
+      <c r="F47" s="4" t="s">
+        <v>10</v>
       </c>
       <c r="G47" s="7" t="s">
         <v>23</v>
@@ -22741,7 +23343,7 @@
         <v>800</v>
       </c>
       <c r="F48" s="5">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>36.75</v>
       </c>
       <c r="G48" s="5" t="s">
@@ -22770,9 +23372,8 @@
       <c r="E49">
         <v>5</v>
       </c>
-      <c r="F49" s="7" t="e">
-        <f t="shared" si="3"/>
-        <v>#VALUE!</v>
+      <c r="F49" s="4" t="s">
+        <v>10</v>
       </c>
       <c r="G49" s="7" t="s">
         <v>23</v>
@@ -22844,6 +23445,15 @@
       <c r="E3" s="4" t="s">
         <v>10</v>
       </c>
+      <c r="F3" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G3" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="H3" s="4" t="s">
+        <v>10</v>
+      </c>
       <c r="I3" t="s">
         <v>94</v>
       </c>
@@ -23167,6 +23777,15 @@
         <v>10</v>
       </c>
       <c r="E15" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F15" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G15" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="H15" s="4" t="s">
         <v>10</v>
       </c>
       <c r="I15" t="s">
@@ -24008,12 +24627,15 @@
       <c r="E46">
         <v>2000</v>
       </c>
-      <c r="F46" s="5" t="e">
-        <f t="shared" si="3"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="G46" s="5"/>
-      <c r="H46" s="7"/>
+      <c r="F46" t="s">
+        <v>10</v>
+      </c>
+      <c r="G46" t="s">
+        <v>10</v>
+      </c>
+      <c r="H46" t="s">
+        <v>10</v>
+      </c>
       <c r="I46" t="s">
         <v>97</v>
       </c>
@@ -24034,12 +24656,15 @@
       <c r="E47">
         <v>375</v>
       </c>
-      <c r="F47" s="7" t="e">
-        <f t="shared" si="3"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="G47" s="7"/>
-      <c r="H47" s="7"/>
+      <c r="F47" t="s">
+        <v>10</v>
+      </c>
+      <c r="G47" t="s">
+        <v>10</v>
+      </c>
+      <c r="H47" t="s">
+        <v>10</v>
+      </c>
       <c r="I47" t="s">
         <v>97</v>
       </c>
@@ -24060,12 +24685,15 @@
       <c r="E48">
         <v>800</v>
       </c>
-      <c r="F48" s="7" t="e">
-        <f t="shared" si="3"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="G48" s="7"/>
-      <c r="H48" s="7"/>
+      <c r="F48" t="s">
+        <v>10</v>
+      </c>
+      <c r="G48" t="s">
+        <v>10</v>
+      </c>
+      <c r="H48" t="s">
+        <v>10</v>
+      </c>
       <c r="I48" t="s">
         <v>97</v>
       </c>
@@ -24121,6 +24749,15 @@
       <c r="E51" s="4" t="s">
         <v>10</v>
       </c>
+      <c r="F51" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G51" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="H51" s="4" t="s">
+        <v>10</v>
+      </c>
       <c r="I51" t="s">
         <v>98</v>
       </c>
@@ -24321,12 +24958,15 @@
       <c r="E58">
         <v>2000</v>
       </c>
-      <c r="F58" s="5" t="e">
-        <f t="shared" si="4"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="G58" s="5"/>
-      <c r="H58" s="7"/>
+      <c r="F58" t="s">
+        <v>10</v>
+      </c>
+      <c r="G58" t="s">
+        <v>10</v>
+      </c>
+      <c r="H58" t="s">
+        <v>10</v>
+      </c>
       <c r="I58" t="s">
         <v>98</v>
       </c>
@@ -24347,12 +24987,15 @@
       <c r="E59">
         <v>375</v>
       </c>
-      <c r="F59" s="7" t="e">
-        <f t="shared" si="4"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="G59" s="7"/>
-      <c r="H59" s="7"/>
+      <c r="F59" t="s">
+        <v>10</v>
+      </c>
+      <c r="G59" t="s">
+        <v>10</v>
+      </c>
+      <c r="H59" t="s">
+        <v>10</v>
+      </c>
       <c r="I59" t="s">
         <v>98</v>
       </c>
@@ -24373,12 +25016,15 @@
       <c r="E60">
         <v>800</v>
       </c>
-      <c r="F60" s="7" t="e">
-        <f t="shared" si="4"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="G60" s="7"/>
-      <c r="H60" s="7"/>
+      <c r="F60" t="s">
+        <v>10</v>
+      </c>
+      <c r="G60" t="s">
+        <v>10</v>
+      </c>
+      <c r="H60" t="s">
+        <v>10</v>
+      </c>
       <c r="I60" t="s">
         <v>98</v>
       </c>
@@ -24434,6 +25080,15 @@
       <c r="E63" s="4" t="s">
         <v>10</v>
       </c>
+      <c r="F63" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G63" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="H63" s="4" t="s">
+        <v>10</v>
+      </c>
       <c r="I63" t="s">
         <v>99</v>
       </c>
@@ -24604,12 +25259,15 @@
       <c r="E69">
         <v>700</v>
       </c>
-      <c r="F69" s="5" t="e">
-        <f t="shared" si="5"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="G69" s="5"/>
-      <c r="H69" s="7"/>
+      <c r="F69" t="s">
+        <v>10</v>
+      </c>
+      <c r="G69" t="s">
+        <v>10</v>
+      </c>
+      <c r="H69" t="s">
+        <v>10</v>
+      </c>
       <c r="I69" t="s">
         <v>99</v>
       </c>
@@ -24630,12 +25288,15 @@
       <c r="E70">
         <v>2000</v>
       </c>
-      <c r="F70" s="5" t="e">
-        <f t="shared" si="5"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="G70" s="5"/>
-      <c r="H70" s="7"/>
+      <c r="F70" t="s">
+        <v>10</v>
+      </c>
+      <c r="G70" t="s">
+        <v>10</v>
+      </c>
+      <c r="H70" t="s">
+        <v>10</v>
+      </c>
       <c r="I70" t="s">
         <v>99</v>
       </c>
@@ -24656,12 +25317,15 @@
       <c r="E71">
         <v>375</v>
       </c>
-      <c r="F71" s="7" t="e">
-        <f t="shared" si="5"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="G71" s="7"/>
-      <c r="H71" s="7"/>
+      <c r="F71" t="s">
+        <v>10</v>
+      </c>
+      <c r="G71" t="s">
+        <v>10</v>
+      </c>
+      <c r="H71" t="s">
+        <v>10</v>
+      </c>
       <c r="I71" t="s">
         <v>99</v>
       </c>
@@ -24682,12 +25346,15 @@
       <c r="E72">
         <v>800</v>
       </c>
-      <c r="F72" s="7" t="e">
-        <f t="shared" si="5"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="G72" s="7"/>
-      <c r="H72" s="7"/>
+      <c r="F72" t="s">
+        <v>10</v>
+      </c>
+      <c r="G72" t="s">
+        <v>10</v>
+      </c>
+      <c r="H72" t="s">
+        <v>10</v>
+      </c>
       <c r="I72" t="s">
         <v>99</v>
       </c>
@@ -24743,6 +25410,15 @@
       <c r="E75" s="4" t="s">
         <v>10</v>
       </c>
+      <c r="F75" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G75" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="H75" s="4" t="s">
+        <v>10</v>
+      </c>
       <c r="I75" t="s">
         <v>100</v>
       </c>
@@ -24973,12 +25649,15 @@
       <c r="E83">
         <v>375</v>
       </c>
-      <c r="F83" s="7" t="e">
-        <f t="shared" si="6"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="G83" s="7"/>
-      <c r="H83" s="7"/>
+      <c r="F83" t="s">
+        <v>10</v>
+      </c>
+      <c r="G83" t="s">
+        <v>10</v>
+      </c>
+      <c r="H83" t="s">
+        <v>10</v>
+      </c>
       <c r="I83" t="s">
         <v>100</v>
       </c>
@@ -24999,12 +25678,15 @@
       <c r="E84">
         <v>800</v>
       </c>
-      <c r="F84" s="7" t="e">
-        <f t="shared" si="6"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="G84" s="7"/>
-      <c r="H84" s="7"/>
+      <c r="F84" t="s">
+        <v>10</v>
+      </c>
+      <c r="G84" t="s">
+        <v>10</v>
+      </c>
+      <c r="H84" t="s">
+        <v>10</v>
+      </c>
       <c r="I84" t="s">
         <v>100</v>
       </c>
@@ -25060,6 +25742,15 @@
       <c r="E87" s="4" t="s">
         <v>10</v>
       </c>
+      <c r="F87" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G87" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="H87" s="4" t="s">
+        <v>10</v>
+      </c>
       <c r="I87" t="s">
         <v>101</v>
       </c>
@@ -25141,7 +25832,7 @@
         <v>150</v>
       </c>
       <c r="F90" s="5">
-        <f t="shared" ref="F90:F97" si="7">(B90/E90)*100</f>
+        <f t="shared" ref="F90:F92" si="7">(B90/E90)*100</f>
         <v>10</v>
       </c>
       <c r="G90" s="5" t="s">
@@ -25170,15 +25861,14 @@
       <c r="E91">
         <v>2.5</v>
       </c>
-      <c r="F91" s="5" t="e">
-        <f t="shared" si="7"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="G91" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="H91" s="5" t="s">
-        <v>20</v>
+      <c r="F91" t="s">
+        <v>10</v>
+      </c>
+      <c r="G91" t="s">
+        <v>10</v>
+      </c>
+      <c r="H91" t="s">
+        <v>10</v>
       </c>
       <c r="I91" t="s">
         <v>101</v>
@@ -25230,12 +25920,15 @@
       <c r="E93">
         <v>700</v>
       </c>
-      <c r="F93" s="5" t="e">
-        <f t="shared" si="7"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="G93" s="5"/>
-      <c r="H93" s="7"/>
+      <c r="F93" t="s">
+        <v>10</v>
+      </c>
+      <c r="G93" t="s">
+        <v>10</v>
+      </c>
+      <c r="H93" t="s">
+        <v>10</v>
+      </c>
       <c r="I93" t="s">
         <v>101</v>
       </c>
@@ -25256,12 +25949,15 @@
       <c r="E94">
         <v>2000</v>
       </c>
-      <c r="F94" s="5" t="e">
-        <f t="shared" si="7"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="G94" s="5"/>
-      <c r="H94" s="7"/>
+      <c r="F94" t="s">
+        <v>10</v>
+      </c>
+      <c r="G94" t="s">
+        <v>10</v>
+      </c>
+      <c r="H94" t="s">
+        <v>10</v>
+      </c>
       <c r="I94" t="s">
         <v>101</v>
       </c>
@@ -25282,12 +25978,15 @@
       <c r="E95">
         <v>375</v>
       </c>
-      <c r="F95" s="7" t="e">
-        <f t="shared" si="7"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="G95" s="7"/>
-      <c r="H95" s="7"/>
+      <c r="F95" t="s">
+        <v>10</v>
+      </c>
+      <c r="G95" t="s">
+        <v>10</v>
+      </c>
+      <c r="H95" t="s">
+        <v>10</v>
+      </c>
       <c r="I95" t="s">
         <v>101</v>
       </c>
@@ -25308,12 +26007,15 @@
       <c r="E96">
         <v>800</v>
       </c>
-      <c r="F96" s="7" t="e">
-        <f t="shared" si="7"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="G96" s="7"/>
-      <c r="H96" s="7"/>
+      <c r="F96" t="s">
+        <v>10</v>
+      </c>
+      <c r="G96" t="s">
+        <v>10</v>
+      </c>
+      <c r="H96" t="s">
+        <v>10</v>
+      </c>
       <c r="I96" t="s">
         <v>101</v>
       </c>
@@ -25334,12 +26036,15 @@
       <c r="E97">
         <v>5</v>
       </c>
-      <c r="F97" s="5" t="e">
-        <f t="shared" si="7"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="G97" s="5"/>
-      <c r="H97" s="5"/>
+      <c r="F97" t="s">
+        <v>10</v>
+      </c>
+      <c r="G97" t="s">
+        <v>10</v>
+      </c>
+      <c r="H97" t="s">
+        <v>10</v>
+      </c>
       <c r="I97" t="s">
         <v>101</v>
       </c>
@@ -25365,6 +26070,15 @@
       <c r="E99" s="4" t="s">
         <v>10</v>
       </c>
+      <c r="F99" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G99" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="H99" s="4" t="s">
+        <v>10</v>
+      </c>
       <c r="I99" t="s">
         <v>104</v>
       </c>
@@ -25446,7 +26160,7 @@
         <v>150</v>
       </c>
       <c r="F102" s="5">
-        <f t="shared" ref="F102:F109" si="8">(B102/E102)*100</f>
+        <f t="shared" ref="F102:F106" si="8">(B102/E102)*100</f>
         <v>10.4</v>
       </c>
       <c r="G102" s="5" t="s">
@@ -25595,12 +26309,15 @@
       <c r="E107">
         <v>375</v>
       </c>
-      <c r="F107" s="7" t="e">
-        <f t="shared" si="8"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="G107" s="7"/>
-      <c r="H107" s="7"/>
+      <c r="F107" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G107" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="H107" s="4" t="s">
+        <v>10</v>
+      </c>
       <c r="I107" t="s">
         <v>104</v>
       </c>
@@ -25621,12 +26338,15 @@
       <c r="E108">
         <v>800</v>
       </c>
-      <c r="F108" s="7" t="e">
-        <f t="shared" si="8"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="G108" s="7"/>
-      <c r="H108" s="7"/>
+      <c r="F108" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G108" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="H108" s="4" t="s">
+        <v>10</v>
+      </c>
       <c r="I108" t="s">
         <v>104</v>
       </c>
@@ -25647,12 +26367,15 @@
       <c r="E109">
         <v>5</v>
       </c>
-      <c r="F109" s="5" t="e">
-        <f t="shared" si="8"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="G109" s="5"/>
-      <c r="H109" s="5"/>
+      <c r="F109" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G109" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="H109" s="4" t="s">
+        <v>10</v>
+      </c>
       <c r="I109" t="s">
         <v>104</v>
       </c>
@@ -25678,6 +26401,15 @@
       <c r="E111" s="4" t="s">
         <v>10</v>
       </c>
+      <c r="F111" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G111" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="H111" s="4" t="s">
+        <v>10</v>
+      </c>
       <c r="I111" t="s">
         <v>105</v>
       </c>
@@ -25759,7 +26491,7 @@
         <v>150</v>
       </c>
       <c r="F114" s="5">
-        <f t="shared" ref="F114:F121" si="9">(B114/E114)*100</f>
+        <f t="shared" ref="F114:F118" si="9">(B114/E114)*100</f>
         <v>11.066666666666668</v>
       </c>
       <c r="G114" s="5" t="s">
@@ -25908,12 +26640,15 @@
       <c r="E119">
         <v>375</v>
       </c>
-      <c r="F119" s="7" t="e">
-        <f t="shared" si="9"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="G119" s="7"/>
-      <c r="H119" s="7"/>
+      <c r="F119" t="s">
+        <v>10</v>
+      </c>
+      <c r="G119" t="s">
+        <v>10</v>
+      </c>
+      <c r="H119" t="s">
+        <v>10</v>
+      </c>
       <c r="I119" t="s">
         <v>105</v>
       </c>
@@ -25934,12 +26669,15 @@
       <c r="E120">
         <v>800</v>
       </c>
-      <c r="F120" s="7" t="e">
-        <f t="shared" si="9"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="G120" s="7"/>
-      <c r="H120" s="7"/>
+      <c r="F120" t="s">
+        <v>10</v>
+      </c>
+      <c r="G120" t="s">
+        <v>10</v>
+      </c>
+      <c r="H120" t="s">
+        <v>10</v>
+      </c>
       <c r="I120" t="s">
         <v>105</v>
       </c>
@@ -25960,12 +26698,15 @@
       <c r="E121">
         <v>5</v>
       </c>
-      <c r="F121" s="5" t="e">
-        <f t="shared" si="9"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="G121" s="5"/>
-      <c r="H121" s="5"/>
+      <c r="F121" t="s">
+        <v>10</v>
+      </c>
+      <c r="G121" t="s">
+        <v>10</v>
+      </c>
+      <c r="H121" t="s">
+        <v>10</v>
+      </c>
       <c r="I121" t="s">
         <v>105</v>
       </c>
@@ -25991,6 +26732,15 @@
       <c r="E123" s="4" t="s">
         <v>10</v>
       </c>
+      <c r="F123" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G123" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="H123" s="4" t="s">
+        <v>10</v>
+      </c>
       <c r="I123" t="s">
         <v>106</v>
       </c>
@@ -26072,7 +26822,7 @@
         <v>150</v>
       </c>
       <c r="F126" s="5">
-        <f t="shared" ref="F126:F133" si="10">(B126/E126)*100</f>
+        <f t="shared" ref="F126:F130" si="10">(B126/E126)*100</f>
         <v>10.666666666666668</v>
       </c>
       <c r="G126" s="5" t="s">
@@ -26221,12 +26971,15 @@
       <c r="E131">
         <v>375</v>
       </c>
-      <c r="F131" s="7" t="e">
-        <f t="shared" si="10"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="G131" s="7"/>
-      <c r="H131" s="7"/>
+      <c r="F131" t="s">
+        <v>10</v>
+      </c>
+      <c r="G131" t="s">
+        <v>10</v>
+      </c>
+      <c r="H131" t="s">
+        <v>10</v>
+      </c>
       <c r="I131" t="s">
         <v>106</v>
       </c>
@@ -26247,12 +27000,15 @@
       <c r="E132">
         <v>800</v>
       </c>
-      <c r="F132" s="7" t="e">
-        <f t="shared" si="10"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="G132" s="7"/>
-      <c r="H132" s="7"/>
+      <c r="F132" t="s">
+        <v>10</v>
+      </c>
+      <c r="G132" t="s">
+        <v>10</v>
+      </c>
+      <c r="H132" t="s">
+        <v>10</v>
+      </c>
       <c r="I132" t="s">
         <v>106</v>
       </c>
@@ -26273,12 +27029,15 @@
       <c r="E133">
         <v>5</v>
       </c>
-      <c r="F133" s="5" t="e">
-        <f t="shared" si="10"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="G133" s="5"/>
-      <c r="H133" s="5"/>
+      <c r="F133" t="s">
+        <v>10</v>
+      </c>
+      <c r="G133" t="s">
+        <v>10</v>
+      </c>
+      <c r="H133" t="s">
+        <v>10</v>
+      </c>
       <c r="I133" t="s">
         <v>106</v>
       </c>
@@ -26304,6 +27063,15 @@
       <c r="E135" s="4" t="s">
         <v>10</v>
       </c>
+      <c r="F135" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G135" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="H135" s="4" t="s">
+        <v>10</v>
+      </c>
       <c r="I135" t="s">
         <v>107</v>
       </c>
@@ -26385,7 +27153,7 @@
         <v>150</v>
       </c>
       <c r="F138" s="5">
-        <f t="shared" ref="F138:F145" si="11">(B138/E138)*100</f>
+        <f t="shared" ref="F138:F142" si="11">(B138/E138)*100</f>
         <v>15.533333333333335</v>
       </c>
       <c r="G138" s="5" t="s">
@@ -26534,12 +27302,15 @@
       <c r="E143">
         <v>375</v>
       </c>
-      <c r="F143" s="7" t="e">
-        <f t="shared" si="11"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="G143" s="7"/>
-      <c r="H143" s="7"/>
+      <c r="F143" t="s">
+        <v>10</v>
+      </c>
+      <c r="G143" t="s">
+        <v>10</v>
+      </c>
+      <c r="H143" t="s">
+        <v>10</v>
+      </c>
       <c r="I143" t="s">
         <v>107</v>
       </c>
@@ -26560,12 +27331,15 @@
       <c r="E144">
         <v>800</v>
       </c>
-      <c r="F144" s="7" t="e">
-        <f t="shared" si="11"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="G144" s="7"/>
-      <c r="H144" s="7"/>
+      <c r="F144" t="s">
+        <v>10</v>
+      </c>
+      <c r="G144" t="s">
+        <v>10</v>
+      </c>
+      <c r="H144" t="s">
+        <v>10</v>
+      </c>
       <c r="I144" t="s">
         <v>107</v>
       </c>
@@ -26586,12 +27360,15 @@
       <c r="E145">
         <v>5</v>
       </c>
-      <c r="F145" s="5" t="e">
-        <f t="shared" si="11"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="G145" s="5"/>
-      <c r="H145" s="5"/>
+      <c r="F145" t="s">
+        <v>10</v>
+      </c>
+      <c r="G145" t="s">
+        <v>10</v>
+      </c>
+      <c r="H145" t="s">
+        <v>10</v>
+      </c>
       <c r="I145" t="s">
         <v>107</v>
       </c>
